--- a/data_generation/andes_cases/ieee39_full_ibrs.xlsx
+++ b/data_generation/andes_cases/ieee39_full_ibrs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10102"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10118"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cloud9/Desktop/ETH Project/Working folder/03_Code/venv/lib/python3.11/site-packages/andes/cases/ieee39/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cloud9/Desktop/ETH Project/Working folder/03_Code/vis-ml/data_generation/andes_cases/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1B779F9-BDDD-8B41-B62F-81DA021D4403}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F203FC6-25B8-6B44-856F-460CE21A41C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-2500" yWindow="-21100" windowWidth="38400" windowHeight="21100" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17180" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Bus" sheetId="1" r:id="rId1"/>
@@ -941,7 +941,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -956,10 +956,9 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5417,7 +5416,6 @@
   <dimension ref="A1:S29"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" style="7"/>
     <col min="6" max="6" width="8.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>

--- a/data_generation/andes_cases/ieee39_full_ibrs.xlsx
+++ b/data_generation/andes_cases/ieee39_full_ibrs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10118"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10208"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cloud9/Desktop/ETH Project/Working folder/03_Code/vis-ml/data_generation/andes_cases/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F203FC6-25B8-6B44-856F-460CE21A41C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{507A1034-FAEC-3243-84D7-0BF09B10759A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17180" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="15000" windowHeight="18900" firstSheet="6" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Bus" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="523" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="527" uniqueCount="269">
   <si>
     <t>idx</t>
   </si>
@@ -3409,7 +3409,7 @@
         <v>205</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D2" t="s">
         <v>205</v>
@@ -3471,7 +3471,7 @@
         <v>206</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D3" t="s">
         <v>206</v>
@@ -3533,7 +3533,7 @@
         <v>207</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D4" t="s">
         <v>207</v>
@@ -3595,7 +3595,7 @@
         <v>208</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D5" t="s">
         <v>208</v>
@@ -3657,7 +3657,7 @@
         <v>209</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6" t="s">
         <v>209</v>
@@ -3719,7 +3719,7 @@
         <v>210</v>
       </c>
       <c r="C7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7" t="s">
         <v>210</v>
@@ -3868,7 +3868,7 @@
         <v>228</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D2" t="s">
         <v>228</v>
@@ -3942,7 +3942,7 @@
         <v>229</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D3" t="s">
         <v>229</v>
@@ -4016,7 +4016,7 @@
         <v>230</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D4" t="s">
         <v>230</v>
@@ -4090,7 +4090,7 @@
         <v>231</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D5" t="s">
         <v>231</v>
@@ -4164,7 +4164,7 @@
         <v>232</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6" t="s">
         <v>232</v>
@@ -4238,7 +4238,7 @@
         <v>233</v>
       </c>
       <c r="C7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7" t="s">
         <v>233</v>
@@ -4772,7 +4772,7 @@
         <v>0.8</v>
       </c>
       <c r="K2">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
@@ -4842,7 +4842,7 @@
         <v>0.8</v>
       </c>
       <c r="K4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
@@ -4877,7 +4877,7 @@
         <v>0.8</v>
       </c>
       <c r="K5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
@@ -4912,7 +4912,7 @@
         <v>0.8</v>
       </c>
       <c r="K6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
@@ -4947,7 +4947,7 @@
         <v>0.8</v>
       </c>
       <c r="K7">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
@@ -4982,7 +4982,7 @@
         <v>0.8</v>
       </c>
       <c r="K8">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
@@ -5017,7 +5017,7 @@
         <v>0.8</v>
       </c>
       <c r="K9">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.2">
@@ -5087,7 +5087,7 @@
         <v>0.8</v>
       </c>
       <c r="K11">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.2">
@@ -5122,7 +5122,7 @@
         <v>0.8</v>
       </c>
       <c r="K12">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
@@ -5157,7 +5157,7 @@
         <v>0.8</v>
       </c>
       <c r="K13">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.2">
@@ -5192,7 +5192,7 @@
         <v>0.8</v>
       </c>
       <c r="K14">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.2">
@@ -5227,7 +5227,7 @@
         <v>0.8</v>
       </c>
       <c r="K15">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.2">
@@ -5262,7 +5262,7 @@
         <v>0.8</v>
       </c>
       <c r="K16">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.2">
@@ -5297,7 +5297,7 @@
         <v>0.8</v>
       </c>
       <c r="K17">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.2">
@@ -5332,7 +5332,7 @@
         <v>0.8</v>
       </c>
       <c r="K18">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.2">
@@ -5367,7 +5367,7 @@
         <v>0.8</v>
       </c>
       <c r="K19">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.2">
@@ -10182,6 +10182,9 @@
       <c r="F2">
         <v>1</v>
       </c>
+      <c r="G2" t="s">
+        <v>268</v>
+      </c>
       <c r="H2">
         <v>1040</v>
       </c>
@@ -10189,10 +10192,10 @@
         <v>50</v>
       </c>
       <c r="J2">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="K2">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -10259,6 +10262,9 @@
       <c r="F3">
         <v>6</v>
       </c>
+      <c r="G3" t="s">
+        <v>268</v>
+      </c>
       <c r="H3">
         <v>1085.7</v>
       </c>
@@ -10266,10 +10272,10 @@
         <v>50</v>
       </c>
       <c r="J3">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="K3">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="L3">
         <v>0</v>
@@ -10336,6 +10342,9 @@
       <c r="F4">
         <v>8</v>
       </c>
+      <c r="G4" t="s">
+        <v>268</v>
+      </c>
       <c r="H4">
         <v>970.2</v>
       </c>
@@ -10343,10 +10352,10 @@
         <v>50</v>
       </c>
       <c r="J4">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="L4">
         <v>0</v>
@@ -10413,6 +10422,9 @@
       <c r="F5">
         <v>9</v>
       </c>
+      <c r="G5" t="s">
+        <v>268</v>
+      </c>
       <c r="H5">
         <v>1684.1</v>
       </c>
@@ -10420,10 +10432,10 @@
         <v>50</v>
       </c>
       <c r="J5">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="L5">
         <v>0</v>
@@ -10472,6 +10484,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data_generation/andes_cases/ieee39_full_ibrs.xlsx
+++ b/data_generation/andes_cases/ieee39_full_ibrs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10208"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10302"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cloud9/Desktop/ETH Project/Working folder/03_Code/vis-ml/data_generation/andes_cases/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{507A1034-FAEC-3243-84D7-0BF09B10759A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28D22FB5-4F69-B641-98CA-1BCC15FA4EA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="15000" windowHeight="18900" firstSheet="6" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="30240" windowHeight="18900" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Bus" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="527" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="530" uniqueCount="272">
   <si>
     <t>idx</t>
   </si>
@@ -852,13 +852,22 @@
   </si>
   <si>
     <t>COI_1</t>
+  </si>
+  <si>
+    <t>rate_a</t>
+  </si>
+  <si>
+    <t>rate_b</t>
+  </si>
+  <si>
+    <t>rate_c</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -886,6 +895,26 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -901,7 +930,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -937,11 +966,67 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFFFFFFF"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFFFFFFF"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thick">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFFFFFFF"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFFFFFFF"/>
+      </right>
+      <top style="thick">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFFFFFFF"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFFFFFFF"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -957,6 +1042,22 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -6287,10 +6388,10 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:X47"/>
+  <dimension ref="A1:AA50"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>13</v>
       </c>
@@ -6363,8 +6464,17 @@
       <c r="X1" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y1" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="Z1" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="AA1" s="12" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="2" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -6384,7 +6494,7 @@
         <v>2</v>
       </c>
       <c r="G2">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="H2">
         <v>50</v>
@@ -6428,8 +6538,17 @@
       <c r="U2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y2" s="11">
+        <v>600</v>
+      </c>
+      <c r="Z2">
+        <v>600</v>
+      </c>
+      <c r="AA2">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="3" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -6449,7 +6568,7 @@
         <v>39</v>
       </c>
       <c r="G3">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="H3">
         <v>50</v>
@@ -6493,8 +6612,17 @@
       <c r="U3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y3" s="11">
+        <v>1000</v>
+      </c>
+      <c r="Z3">
+        <v>1000</v>
+      </c>
+      <c r="AA3">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -6514,7 +6642,7 @@
         <v>3</v>
       </c>
       <c r="G4">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="H4">
         <v>50</v>
@@ -6558,8 +6686,17 @@
       <c r="U4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y4" s="11">
+        <v>500</v>
+      </c>
+      <c r="Z4">
+        <v>500</v>
+      </c>
+      <c r="AA4">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -6579,7 +6716,7 @@
         <v>25</v>
       </c>
       <c r="G5">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="H5">
         <v>50</v>
@@ -6623,8 +6760,17 @@
       <c r="U5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y5" s="11">
+        <v>500</v>
+      </c>
+      <c r="Z5">
+        <v>500</v>
+      </c>
+      <c r="AA5">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -6644,7 +6790,7 @@
         <v>4</v>
       </c>
       <c r="G6">
-        <v>100</v>
+        <v>900</v>
       </c>
       <c r="H6">
         <v>50</v>
@@ -6688,8 +6834,17 @@
       <c r="U6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y6" s="11">
+        <v>900</v>
+      </c>
+      <c r="Z6">
+        <v>900</v>
+      </c>
+      <c r="AA6">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -6709,7 +6864,7 @@
         <v>18</v>
       </c>
       <c r="G7">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="H7">
         <v>50</v>
@@ -6753,8 +6908,17 @@
       <c r="U7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y7" s="11">
+        <v>500</v>
+      </c>
+      <c r="Z7">
+        <v>500</v>
+      </c>
+      <c r="AA7">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -6774,7 +6938,7 @@
         <v>5</v>
       </c>
       <c r="G8">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="H8">
         <v>50</v>
@@ -6818,8 +6982,17 @@
       <c r="U8">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y8" s="11">
+        <v>500</v>
+      </c>
+      <c r="Z8">
+        <v>500</v>
+      </c>
+      <c r="AA8">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -6839,7 +7012,7 @@
         <v>14</v>
       </c>
       <c r="G9">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="H9">
         <v>50</v>
@@ -6883,8 +7056,17 @@
       <c r="U9">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y9" s="11">
+        <v>600</v>
+      </c>
+      <c r="Z9">
+        <v>600</v>
+      </c>
+      <c r="AA9">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -6904,7 +7086,7 @@
         <v>6</v>
       </c>
       <c r="G10">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="H10">
         <v>50</v>
@@ -6948,8 +7130,17 @@
       <c r="U10">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y10" s="11">
+        <v>500</v>
+      </c>
+      <c r="Z10">
+        <v>500</v>
+      </c>
+      <c r="AA10">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>9</v>
       </c>
@@ -6969,7 +7160,7 @@
         <v>8</v>
       </c>
       <c r="G11">
-        <v>100</v>
+        <v>1200</v>
       </c>
       <c r="H11">
         <v>50</v>
@@ -7013,8 +7204,17 @@
       <c r="U11">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y11" s="11">
+        <v>1200</v>
+      </c>
+      <c r="Z11">
+        <v>1200</v>
+      </c>
+      <c r="AA11">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <v>10</v>
       </c>
@@ -7034,7 +7234,7 @@
         <v>7</v>
       </c>
       <c r="G12">
-        <v>100</v>
+        <v>900</v>
       </c>
       <c r="H12">
         <v>50</v>
@@ -7078,8 +7278,17 @@
       <c r="U12">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y12" s="11">
+        <v>900</v>
+      </c>
+      <c r="Z12">
+        <v>900</v>
+      </c>
+      <c r="AA12">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>11</v>
       </c>
@@ -7099,7 +7308,7 @@
         <v>11</v>
       </c>
       <c r="G13">
-        <v>100</v>
+        <v>900</v>
       </c>
       <c r="H13">
         <v>50</v>
@@ -7143,8 +7352,17 @@
       <c r="U13">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y13" s="11">
+        <v>900</v>
+      </c>
+      <c r="Z13">
+        <v>900</v>
+      </c>
+      <c r="AA13">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <v>12</v>
       </c>
@@ -7164,7 +7382,7 @@
         <v>8</v>
       </c>
       <c r="G14">
-        <v>100</v>
+        <v>480</v>
       </c>
       <c r="H14">
         <v>50</v>
@@ -7208,8 +7426,17 @@
       <c r="U14">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y14" s="11">
+        <v>480</v>
+      </c>
+      <c r="Z14">
+        <v>480</v>
+      </c>
+      <c r="AA14">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <v>13</v>
       </c>
@@ -7229,7 +7456,7 @@
         <v>9</v>
       </c>
       <c r="G15">
-        <v>100</v>
+        <v>1800</v>
       </c>
       <c r="H15">
         <v>50</v>
@@ -7273,8 +7500,17 @@
       <c r="U15">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y15" s="11">
+        <v>1800</v>
+      </c>
+      <c r="Z15">
+        <v>1800</v>
+      </c>
+      <c r="AA15">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
         <v>14</v>
       </c>
@@ -7294,7 +7530,7 @@
         <v>39</v>
       </c>
       <c r="G16">
-        <v>100</v>
+        <v>900</v>
       </c>
       <c r="H16">
         <v>50</v>
@@ -7338,8 +7574,17 @@
       <c r="U16">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="Y16" s="11">
+        <v>900</v>
+      </c>
+      <c r="Z16">
+        <v>900</v>
+      </c>
+      <c r="AA16">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="17" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
         <v>15</v>
       </c>
@@ -7359,7 +7604,7 @@
         <v>11</v>
       </c>
       <c r="G17">
-        <v>100</v>
+        <v>900</v>
       </c>
       <c r="H17">
         <v>50</v>
@@ -7403,8 +7648,17 @@
       <c r="U17">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="Y17" s="11">
+        <v>900</v>
+      </c>
+      <c r="Z17">
+        <v>900</v>
+      </c>
+      <c r="AA17">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="18" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
         <v>16</v>
       </c>
@@ -7424,7 +7678,7 @@
         <v>13</v>
       </c>
       <c r="G18">
-        <v>100</v>
+        <v>900</v>
       </c>
       <c r="H18">
         <v>50</v>
@@ -7468,8 +7722,17 @@
       <c r="U18">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="Y18" s="11">
+        <v>900</v>
+      </c>
+      <c r="Z18">
+        <v>900</v>
+      </c>
+      <c r="AA18">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="19" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
         <v>17</v>
       </c>
@@ -7489,7 +7752,7 @@
         <v>14</v>
       </c>
       <c r="G19">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="H19">
         <v>50</v>
@@ -7533,8 +7796,17 @@
       <c r="U19">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="Y19" s="11">
+        <v>600</v>
+      </c>
+      <c r="Z19">
+        <v>600</v>
+      </c>
+      <c r="AA19">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="20" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
         <v>18</v>
       </c>
@@ -7554,7 +7826,7 @@
         <v>15</v>
       </c>
       <c r="G20">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="H20">
         <v>50</v>
@@ -7598,8 +7870,17 @@
       <c r="U20">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="Y20" s="11">
+        <v>600</v>
+      </c>
+      <c r="Z20">
+        <v>600</v>
+      </c>
+      <c r="AA20">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="21" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
         <v>19</v>
       </c>
@@ -7619,7 +7900,7 @@
         <v>16</v>
       </c>
       <c r="G21">
-        <v>100</v>
+        <v>900</v>
       </c>
       <c r="H21">
         <v>50</v>
@@ -7663,8 +7944,17 @@
       <c r="U21">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="Y21" s="11">
+        <v>900</v>
+      </c>
+      <c r="Z21">
+        <v>900</v>
+      </c>
+      <c r="AA21">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="22" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
         <v>20</v>
       </c>
@@ -7684,7 +7974,7 @@
         <v>17</v>
       </c>
       <c r="G22">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="H22">
         <v>50</v>
@@ -7728,8 +8018,17 @@
       <c r="U22">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="Y22" s="11">
+        <v>500</v>
+      </c>
+      <c r="Z22">
+        <v>500</v>
+      </c>
+      <c r="AA22">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="23" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
         <v>21</v>
       </c>
@@ -7749,7 +8048,7 @@
         <v>19</v>
       </c>
       <c r="G23">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="H23">
         <v>50</v>
@@ -7793,8 +8092,17 @@
       <c r="U23">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="Y23" s="11">
+        <v>500</v>
+      </c>
+      <c r="Z23">
+        <v>500</v>
+      </c>
+      <c r="AA23">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="24" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
         <v>22</v>
       </c>
@@ -7814,7 +8122,7 @@
         <v>21</v>
       </c>
       <c r="G24">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="H24">
         <v>50</v>
@@ -7858,8 +8166,17 @@
       <c r="U24">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="Y24" s="11">
+        <v>600</v>
+      </c>
+      <c r="Z24">
+        <v>600</v>
+      </c>
+      <c r="AA24">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="25" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
         <v>23</v>
       </c>
@@ -7879,7 +8196,7 @@
         <v>24</v>
       </c>
       <c r="G25">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="H25">
         <v>50</v>
@@ -7923,8 +8240,17 @@
       <c r="U25">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="Y25" s="11">
+        <v>600</v>
+      </c>
+      <c r="Z25">
+        <v>600</v>
+      </c>
+      <c r="AA25">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="26" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
         <v>24</v>
       </c>
@@ -7944,7 +8270,7 @@
         <v>18</v>
       </c>
       <c r="G26">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="H26">
         <v>50</v>
@@ -7988,8 +8314,17 @@
       <c r="U26">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="Y26" s="11">
+        <v>600</v>
+      </c>
+      <c r="Z26">
+        <v>600</v>
+      </c>
+      <c r="AA26">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="27" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A27" s="1">
         <v>25</v>
       </c>
@@ -8009,7 +8344,7 @@
         <v>27</v>
       </c>
       <c r="G27">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="H27">
         <v>50</v>
@@ -8053,8 +8388,17 @@
       <c r="U27">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="Y27" s="11">
+        <v>600</v>
+      </c>
+      <c r="Z27">
+        <v>600</v>
+      </c>
+      <c r="AA27">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="28" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
         <v>26</v>
       </c>
@@ -8074,7 +8418,7 @@
         <v>22</v>
       </c>
       <c r="G28">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="H28">
         <v>50</v>
@@ -8118,8 +8462,17 @@
       <c r="U28">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="Y28" s="11">
+        <v>600</v>
+      </c>
+      <c r="Z28">
+        <v>600</v>
+      </c>
+      <c r="AA28">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="29" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A29" s="1">
         <v>27</v>
       </c>
@@ -8139,7 +8492,7 @@
         <v>23</v>
       </c>
       <c r="G29">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="H29">
         <v>50</v>
@@ -8183,8 +8536,17 @@
       <c r="U29">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="Y29" s="11">
+        <v>600</v>
+      </c>
+      <c r="Z29">
+        <v>600</v>
+      </c>
+      <c r="AA29">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="30" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A30" s="1">
         <v>28</v>
       </c>
@@ -8204,7 +8566,7 @@
         <v>24</v>
       </c>
       <c r="G30">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="H30">
         <v>50</v>
@@ -8248,8 +8610,17 @@
       <c r="U30">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="Y30" s="11">
+        <v>600</v>
+      </c>
+      <c r="Z30">
+        <v>600</v>
+      </c>
+      <c r="AA30">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="31" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A31" s="1">
         <v>29</v>
       </c>
@@ -8269,7 +8640,7 @@
         <v>26</v>
       </c>
       <c r="G31">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="H31">
         <v>50</v>
@@ -8313,8 +8684,17 @@
       <c r="U31">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="Y31" s="11">
+        <v>600</v>
+      </c>
+      <c r="Z31">
+        <v>600</v>
+      </c>
+      <c r="AA31">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="32" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A32" s="1">
         <v>30</v>
       </c>
@@ -8334,7 +8714,7 @@
         <v>27</v>
       </c>
       <c r="G32">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="H32">
         <v>50</v>
@@ -8378,8 +8758,17 @@
       <c r="U32">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="Y32" s="11">
+        <v>600</v>
+      </c>
+      <c r="Z32">
+        <v>600</v>
+      </c>
+      <c r="AA32">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="33" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A33" s="1">
         <v>31</v>
       </c>
@@ -8399,7 +8788,7 @@
         <v>28</v>
       </c>
       <c r="G33">
-        <v>100</v>
+        <v>900</v>
       </c>
       <c r="H33">
         <v>50</v>
@@ -8443,8 +8832,17 @@
       <c r="U33">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="Y33" s="11">
+        <v>900</v>
+      </c>
+      <c r="Z33">
+        <v>900</v>
+      </c>
+      <c r="AA33">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="34" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A34" s="1">
         <v>32</v>
       </c>
@@ -8464,7 +8862,7 @@
         <v>29</v>
       </c>
       <c r="G34">
-        <v>100</v>
+        <v>900</v>
       </c>
       <c r="H34">
         <v>50</v>
@@ -8508,8 +8906,17 @@
       <c r="U34">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="Y34" s="11">
+        <v>900</v>
+      </c>
+      <c r="Z34">
+        <v>900</v>
+      </c>
+      <c r="AA34">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="35" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A35" s="1">
         <v>33</v>
       </c>
@@ -8529,7 +8936,7 @@
         <v>29</v>
       </c>
       <c r="G35">
-        <v>100</v>
+        <v>900</v>
       </c>
       <c r="H35">
         <v>50</v>
@@ -8573,8 +8980,17 @@
       <c r="U35">
         <v>0</v>
       </c>
-    </row>
-    <row r="36" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="Y35" s="11">
+        <v>900</v>
+      </c>
+      <c r="Z35">
+        <v>900</v>
+      </c>
+      <c r="AA35">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="36" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A36" s="1">
         <v>34</v>
       </c>
@@ -8594,7 +9010,7 @@
         <v>30</v>
       </c>
       <c r="G36">
-        <v>100</v>
+        <v>900</v>
       </c>
       <c r="H36">
         <v>50</v>
@@ -8638,8 +9054,17 @@
       <c r="U36">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="Y36" s="11">
+        <v>900</v>
+      </c>
+      <c r="Z36">
+        <v>900</v>
+      </c>
+      <c r="AA36">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="37" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A37" s="1">
         <v>35</v>
       </c>
@@ -8659,7 +9084,7 @@
         <v>6</v>
       </c>
       <c r="G37">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="H37">
         <v>50</v>
@@ -8703,8 +9128,17 @@
       <c r="U37">
         <v>0</v>
       </c>
-    </row>
-    <row r="38" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="Y37" s="11">
+        <v>600</v>
+      </c>
+      <c r="Z37">
+        <v>600</v>
+      </c>
+      <c r="AA37">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="38" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A38" s="1">
         <v>36</v>
       </c>
@@ -8724,7 +9158,7 @@
         <v>32</v>
       </c>
       <c r="G38">
-        <v>100</v>
+        <v>900</v>
       </c>
       <c r="H38">
         <v>50</v>
@@ -8768,8 +9202,17 @@
       <c r="U38">
         <v>0</v>
       </c>
-    </row>
-    <row r="39" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="Y38" s="11">
+        <v>900</v>
+      </c>
+      <c r="Z38">
+        <v>900</v>
+      </c>
+      <c r="AA38">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="39" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A39" s="1">
         <v>37</v>
       </c>
@@ -8789,7 +9232,7 @@
         <v>11</v>
       </c>
       <c r="G39">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="H39">
         <v>50</v>
@@ -8833,8 +9276,17 @@
       <c r="U39">
         <v>0</v>
       </c>
-    </row>
-    <row r="40" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="Y39" s="11">
+        <v>600</v>
+      </c>
+      <c r="Z39">
+        <v>600</v>
+      </c>
+      <c r="AA39">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="40" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A40" s="1">
         <v>38</v>
       </c>
@@ -8854,7 +9306,7 @@
         <v>13</v>
       </c>
       <c r="G40">
-        <v>100</v>
+        <v>900</v>
       </c>
       <c r="H40">
         <v>50</v>
@@ -8898,8 +9350,17 @@
       <c r="U40">
         <v>0</v>
       </c>
-    </row>
-    <row r="41" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="Y40" s="11">
+        <v>900</v>
+      </c>
+      <c r="Z40">
+        <v>900</v>
+      </c>
+      <c r="AA40">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="41" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A41" s="1">
         <v>39</v>
       </c>
@@ -8919,7 +9380,7 @@
         <v>20</v>
       </c>
       <c r="G41">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="H41">
         <v>50</v>
@@ -8963,8 +9424,17 @@
       <c r="U41">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="Y41" s="11">
+        <v>600</v>
+      </c>
+      <c r="Z41">
+        <v>600</v>
+      </c>
+      <c r="AA41">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="42" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A42" s="1">
         <v>40</v>
       </c>
@@ -8984,7 +9454,7 @@
         <v>33</v>
       </c>
       <c r="G42">
-        <v>100</v>
+        <v>900</v>
       </c>
       <c r="H42">
         <v>50</v>
@@ -9028,8 +9498,17 @@
       <c r="U42">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="Y42" s="11">
+        <v>900</v>
+      </c>
+      <c r="Z42">
+        <v>900</v>
+      </c>
+      <c r="AA42">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="43" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A43" s="1">
         <v>41</v>
       </c>
@@ -9049,7 +9528,7 @@
         <v>34</v>
       </c>
       <c r="G43">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="H43">
         <v>50</v>
@@ -9093,8 +9572,17 @@
       <c r="U43">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="Y43" s="11">
+        <v>600</v>
+      </c>
+      <c r="Z43">
+        <v>600</v>
+      </c>
+      <c r="AA43">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="44" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A44" s="1">
         <v>42</v>
       </c>
@@ -9114,7 +9602,7 @@
         <v>35</v>
       </c>
       <c r="G44">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="H44">
         <v>50</v>
@@ -9158,8 +9646,17 @@
       <c r="U44">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="Y44" s="11">
+        <v>600</v>
+      </c>
+      <c r="Z44">
+        <v>600</v>
+      </c>
+      <c r="AA44">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="45" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A45" s="1">
         <v>43</v>
       </c>
@@ -9179,7 +9676,7 @@
         <v>36</v>
       </c>
       <c r="G45">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="H45">
         <v>50</v>
@@ -9223,8 +9720,17 @@
       <c r="U45">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="Y45" s="11">
+        <v>600</v>
+      </c>
+      <c r="Z45">
+        <v>600</v>
+      </c>
+      <c r="AA45">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="46" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A46" s="1">
         <v>44</v>
       </c>
@@ -9244,7 +9750,7 @@
         <v>37</v>
       </c>
       <c r="G46">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="H46">
         <v>50</v>
@@ -9288,8 +9794,17 @@
       <c r="U46">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="Y46" s="11">
+        <v>600</v>
+      </c>
+      <c r="Z46">
+        <v>600</v>
+      </c>
+      <c r="AA46">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="47" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A47" s="1">
         <v>45</v>
       </c>
@@ -9309,7 +9824,7 @@
         <v>38</v>
       </c>
       <c r="G47">
-        <v>100</v>
+        <v>1200</v>
       </c>
       <c r="H47">
         <v>50</v>
@@ -9353,6 +9868,18 @@
       <c r="U47">
         <v>0</v>
       </c>
+      <c r="Y47" s="11">
+        <v>1200</v>
+      </c>
+      <c r="Z47">
+        <v>1200</v>
+      </c>
+      <c r="AA47">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="50" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E50" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10080,7 +10607,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7388A490-0195-AD4B-9DED-7B8527B5ECA5}">
-  <dimension ref="A1:Z5"/>
+  <dimension ref="A1:Z18"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:26" x14ac:dyDescent="0.2">
@@ -10483,6 +11010,19 @@
         <v>0</v>
       </c>
     </row>
+    <row r="14" spans="1:26" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="15" spans="1:26" ht="24" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="J15" s="7"/>
+    </row>
+    <row r="16" spans="1:26" ht="25" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="J16" s="8"/>
+    </row>
+    <row r="17" spans="10:10" ht="24" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="J17" s="9"/>
+    </row>
+    <row r="18" spans="10:10" ht="24" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="J18" s="9"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data_generation/andes_cases/ieee39_full_ibrs.xlsx
+++ b/data_generation/andes_cases/ieee39_full_ibrs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10302"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10328"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cloud9/Desktop/ETH Project/Working folder/03_Code/vis-ml/data_generation/andes_cases/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28D22FB5-4F69-B641-98CA-1BCC15FA4EA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F27BE91F-D6FB-914E-9DF7-0A469826DB5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="30240" windowHeight="18900" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20" yWindow="760" windowWidth="30240" windowHeight="17180" firstSheet="1" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Bus" sheetId="1" r:id="rId1"/>
@@ -21,31 +21,26 @@
     <sheet name="Line" sheetId="6" r:id="rId6"/>
     <sheet name="Area" sheetId="7" r:id="rId7"/>
     <sheet name="GENROU" sheetId="8" r:id="rId8"/>
-    <sheet name="REGCV1" sheetId="15" r:id="rId9"/>
-    <sheet name="TGOV1N" sheetId="9" r:id="rId10"/>
-    <sheet name="IEEEX1" sheetId="10" r:id="rId11"/>
-    <sheet name="IEEEST" sheetId="11" r:id="rId12"/>
-    <sheet name="BusFreq" sheetId="12" r:id="rId13"/>
-    <sheet name="COI" sheetId="13" r:id="rId14"/>
-    <sheet name="Toggler" sheetId="14" r:id="rId15"/>
+    <sheet name="REGCV1" sheetId="9" r:id="rId9"/>
+    <sheet name="TGOV1N" sheetId="10" r:id="rId10"/>
+    <sheet name="TGOV1" sheetId="11" r:id="rId11"/>
+    <sheet name="IEESGO" sheetId="12" r:id="rId12"/>
+    <sheet name="GAST" sheetId="13" r:id="rId13"/>
+    <sheet name="IEEEX1" sheetId="14" r:id="rId14"/>
+    <sheet name="IEEEST" sheetId="15" r:id="rId15"/>
+    <sheet name="BusFreq" sheetId="16" r:id="rId16"/>
+    <sheet name="BusROCOF" sheetId="17" r:id="rId17"/>
+    <sheet name="COI" sheetId="18" r:id="rId18"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="530" uniqueCount="272">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="712" uniqueCount="367">
+  <si>
+    <t>uid</t>
+  </si>
   <si>
     <t>idx</t>
   </si>
@@ -56,6 +51,72 @@
     <t>name</t>
   </si>
   <si>
+    <t>syn</t>
+  </si>
+  <si>
+    <t>Tn</t>
+  </si>
+  <si>
+    <t>wref0</t>
+  </si>
+  <si>
+    <t>R</t>
+  </si>
+  <si>
+    <t>VMAX</t>
+  </si>
+  <si>
+    <t>VMIN</t>
+  </si>
+  <si>
+    <t>T1</t>
+  </si>
+  <si>
+    <t>T2</t>
+  </si>
+  <si>
+    <t>T3</t>
+  </si>
+  <si>
+    <t>Dt</t>
+  </si>
+  <si>
+    <t>TGOV1_2</t>
+  </si>
+  <si>
+    <t>GENROU_2</t>
+  </si>
+  <si>
+    <t>TGOV1_3</t>
+  </si>
+  <si>
+    <t>GENROU_3</t>
+  </si>
+  <si>
+    <t>TGOV1_4</t>
+  </si>
+  <si>
+    <t>GENROU_4</t>
+  </si>
+  <si>
+    <t>TGOV1_5</t>
+  </si>
+  <si>
+    <t>GENROU_5</t>
+  </si>
+  <si>
+    <t>TGOV1_7</t>
+  </si>
+  <si>
+    <t>GENROU_7</t>
+  </si>
+  <si>
+    <t>TGOV1_10</t>
+  </si>
+  <si>
+    <t>GENROU_10</t>
+  </si>
+  <si>
     <t>Vn</t>
   </si>
   <si>
@@ -86,9 +147,6 @@
     <t>owner</t>
   </si>
   <si>
-    <t>uid</t>
-  </si>
-  <si>
     <t>BUS1</t>
   </si>
   <si>
@@ -350,6 +408,15 @@
     <t>phi</t>
   </si>
   <si>
+    <t>rate_a</t>
+  </si>
+  <si>
+    <t>rate_b</t>
+  </si>
+  <si>
+    <t>rate_c</t>
+  </si>
+  <si>
     <t>Line_1</t>
   </si>
   <si>
@@ -500,6 +567,9 @@
     <t>coi</t>
   </si>
   <si>
+    <t>coi2</t>
+  </si>
+  <si>
     <t>D</t>
   </si>
   <si>
@@ -524,6 +594,12 @@
     <t>S12</t>
   </si>
   <si>
+    <t>gammap</t>
+  </si>
+  <si>
+    <t>gammaq</t>
+  </si>
+  <si>
     <t>xd</t>
   </si>
   <si>
@@ -551,70 +627,115 @@
     <t>Tq20</t>
   </si>
   <si>
-    <t>GENROU_2</t>
-  </si>
-  <si>
-    <t>GENROU_3</t>
-  </si>
-  <si>
-    <t>GENROU_4</t>
-  </si>
-  <si>
-    <t>GENROU_5</t>
-  </si>
-  <si>
-    <t>GENROU_7</t>
-  </si>
-  <si>
-    <t>GENROU_10</t>
-  </si>
-  <si>
-    <t>syn</t>
-  </si>
-  <si>
-    <t>Tn</t>
-  </si>
-  <si>
-    <t>wref0</t>
-  </si>
-  <si>
-    <t>R</t>
-  </si>
-  <si>
-    <t>VMAX</t>
-  </si>
-  <si>
-    <t>VMIN</t>
-  </si>
-  <si>
-    <t>T1</t>
-  </si>
-  <si>
-    <t>T2</t>
-  </si>
-  <si>
-    <t>T3</t>
-  </si>
-  <si>
-    <t>Dt</t>
-  </si>
-  <si>
-    <t>TGOV1_2</t>
-  </si>
-  <si>
-    <t>TGOV1_3</t>
-  </si>
-  <si>
-    <t>TGOV1_4</t>
-  </si>
-  <si>
-    <t>TGOV1_5</t>
-  </si>
-  <si>
-    <t>TGOV1_7</t>
-  </si>
-  <si>
-    <t>TGOV1_10</t>
+    <t>COI_1</t>
+  </si>
+  <si>
+    <t>Tc</t>
+  </si>
+  <si>
+    <t>kv</t>
+  </si>
+  <si>
+    <t>Kpvd</t>
+  </si>
+  <si>
+    <t>Kivd</t>
+  </si>
+  <si>
+    <t>Kpvq</t>
+  </si>
+  <si>
+    <t>Kivq</t>
+  </si>
+  <si>
+    <t>KpId</t>
+  </si>
+  <si>
+    <t>KiId</t>
+  </si>
+  <si>
+    <t>KpIq</t>
+  </si>
+  <si>
+    <t>KiIq</t>
+  </si>
+  <si>
+    <t>REGCV1_1</t>
+  </si>
+  <si>
+    <t>REGCV1_2</t>
+  </si>
+  <si>
+    <t>REGCV1_3</t>
+  </si>
+  <si>
+    <t>REGCV1_4</t>
+  </si>
+  <si>
+    <t>T4</t>
+  </si>
+  <si>
+    <t>T5</t>
+  </si>
+  <si>
+    <t>T6</t>
+  </si>
+  <si>
+    <t>K1</t>
+  </si>
+  <si>
+    <t>K2</t>
+  </si>
+  <si>
+    <t>K3</t>
+  </si>
+  <si>
+    <t>PMAX</t>
+  </si>
+  <si>
+    <t>PMIN</t>
+  </si>
+  <si>
+    <t>IEESGO_2</t>
+  </si>
+  <si>
+    <t>IEESGO_3</t>
+  </si>
+  <si>
+    <t>IEESGO_4</t>
+  </si>
+  <si>
+    <t>IEESGO_5</t>
+  </si>
+  <si>
+    <t>IEESGO_7</t>
+  </si>
+  <si>
+    <t>IEESGO_10</t>
+  </si>
+  <si>
+    <t>KT</t>
+  </si>
+  <si>
+    <t>AT</t>
+  </si>
+  <si>
+    <t>GAST_2</t>
+  </si>
+  <si>
+    <t>GAST_3</t>
+  </si>
+  <si>
+    <t>GAST_4</t>
+  </si>
+  <si>
+    <t>GAST_5</t>
+  </si>
+  <si>
+    <t>GAST_7</t>
+  </si>
+  <si>
+    <t>GAST_10</t>
   </si>
   <si>
     <t>TR</t>
@@ -707,15 +828,6 @@
     <t>A6</t>
   </si>
   <si>
-    <t>T4</t>
-  </si>
-  <si>
-    <t>T5</t>
-  </si>
-  <si>
-    <t>T6</t>
-  </si>
-  <si>
     <t>KS</t>
   </si>
   <si>
@@ -734,140 +846,305 @@
     <t>IEEEST_2</t>
   </si>
   <si>
+    <t>BusFreq_2</t>
+  </si>
+  <si>
     <t>IEEEST_3</t>
   </si>
   <si>
+    <t>BusFreq_3</t>
+  </si>
+  <si>
     <t>IEEEST_4</t>
   </si>
   <si>
+    <t>BusFreq_4</t>
+  </si>
+  <si>
     <t>IEEEST_5</t>
   </si>
   <si>
+    <t>BusFreq_5</t>
+  </si>
+  <si>
     <t>IEEEST_7</t>
   </si>
   <si>
+    <t>BusFreq_7</t>
+  </si>
+  <si>
     <t>IEEEST_10</t>
   </si>
   <si>
+    <t>BusFreq_10</t>
+  </si>
+  <si>
+    <t>Tf</t>
+  </si>
+  <si>
+    <t>Tw</t>
+  </si>
+  <si>
     <t>BusFreq_1</t>
   </si>
   <si>
-    <t>BusFreq_2</t>
-  </si>
-  <si>
-    <t>BusFreq_3</t>
-  </si>
-  <si>
-    <t>BusFreq_4</t>
-  </si>
-  <si>
-    <t>BusFreq_5</t>
-  </si>
-  <si>
     <t>BusFreq_6</t>
   </si>
   <si>
-    <t>BusFreq_7</t>
-  </si>
-  <si>
     <t>BusFreq_8</t>
   </si>
   <si>
     <t>BusFreq_9</t>
   </si>
   <si>
-    <t>BusFreq_10</t>
-  </si>
-  <si>
-    <t>Tf</t>
-  </si>
-  <si>
-    <t>Tw</t>
-  </si>
-  <si>
-    <t>model</t>
-  </si>
-  <si>
-    <t>dev</t>
-  </si>
-  <si>
-    <t>t</t>
-  </si>
-  <si>
-    <t>Toggler_1</t>
-  </si>
-  <si>
-    <t>GENROU</t>
-  </si>
-  <si>
-    <t>coi2</t>
-  </si>
-  <si>
-    <t>Tc</t>
-  </si>
-  <si>
-    <t>gammap</t>
-  </si>
-  <si>
-    <t>gammaq</t>
-  </si>
-  <si>
-    <t>Kpvd</t>
-  </si>
-  <si>
-    <t>Kivd</t>
-  </si>
-  <si>
-    <t>Kpvq</t>
-  </si>
-  <si>
-    <t>Kivq</t>
-  </si>
-  <si>
-    <t>KpId</t>
-  </si>
-  <si>
-    <t>KiId</t>
-  </si>
-  <si>
-    <t>KpIq</t>
-  </si>
-  <si>
-    <t>KiIq</t>
-  </si>
-  <si>
-    <t>REGCV1_1</t>
-  </si>
-  <si>
-    <t>REGCV1_2</t>
-  </si>
-  <si>
-    <t>REGCV1_3</t>
-  </si>
-  <si>
-    <t>REGCV1_4</t>
-  </si>
-  <si>
-    <t>kv</t>
-  </si>
-  <si>
-    <t>COI_1</t>
-  </si>
-  <si>
-    <t>rate_a</t>
-  </si>
-  <si>
-    <t>rate_b</t>
-  </si>
-  <si>
-    <t>rate_c</t>
+    <t>Tr</t>
+  </si>
+  <si>
+    <t>BusROCOF_1</t>
+  </si>
+  <si>
+    <t>BusROCOF 1</t>
+  </si>
+  <si>
+    <t>BusROCOF_2</t>
+  </si>
+  <si>
+    <t>BusROCOF 2</t>
+  </si>
+  <si>
+    <t>BusROCOF_3</t>
+  </si>
+  <si>
+    <t>BusROCOF 3</t>
+  </si>
+  <si>
+    <t>BusROCOF_4</t>
+  </si>
+  <si>
+    <t>BusROCOF 4</t>
+  </si>
+  <si>
+    <t>BusROCOF_5</t>
+  </si>
+  <si>
+    <t>BusROCOF 5</t>
+  </si>
+  <si>
+    <t>BusROCOF_6</t>
+  </si>
+  <si>
+    <t>BusROCOF 6</t>
+  </si>
+  <si>
+    <t>BusROCOF_7</t>
+  </si>
+  <si>
+    <t>BusROCOF 7</t>
+  </si>
+  <si>
+    <t>BusROCOF_8</t>
+  </si>
+  <si>
+    <t>BusROCOF 8</t>
+  </si>
+  <si>
+    <t>BusROCOF_9</t>
+  </si>
+  <si>
+    <t>BusROCOF 9</t>
+  </si>
+  <si>
+    <t>BusROCOF_10</t>
+  </si>
+  <si>
+    <t>BusROCOF 10</t>
+  </si>
+  <si>
+    <t>BusROCOF_11</t>
+  </si>
+  <si>
+    <t>BusROCOF 11</t>
+  </si>
+  <si>
+    <t>BusROCOF_12</t>
+  </si>
+  <si>
+    <t>BusROCOF 12</t>
+  </si>
+  <si>
+    <t>BusROCOF_13</t>
+  </si>
+  <si>
+    <t>BusROCOF 13</t>
+  </si>
+  <si>
+    <t>BusROCOF_14</t>
+  </si>
+  <si>
+    <t>BusROCOF 14</t>
+  </si>
+  <si>
+    <t>BusROCOF_15</t>
+  </si>
+  <si>
+    <t>BusROCOF 15</t>
+  </si>
+  <si>
+    <t>BusROCOF_16</t>
+  </si>
+  <si>
+    <t>BusROCOF 16</t>
+  </si>
+  <si>
+    <t>BusROCOF_17</t>
+  </si>
+  <si>
+    <t>BusROCOF 17</t>
+  </si>
+  <si>
+    <t>BusROCOF_18</t>
+  </si>
+  <si>
+    <t>BusROCOF 18</t>
+  </si>
+  <si>
+    <t>BusROCOF_19</t>
+  </si>
+  <si>
+    <t>BusROCOF 19</t>
+  </si>
+  <si>
+    <t>BusROCOF_20</t>
+  </si>
+  <si>
+    <t>BusROCOF 20</t>
+  </si>
+  <si>
+    <t>BusROCOF_21</t>
+  </si>
+  <si>
+    <t>BusROCOF 21</t>
+  </si>
+  <si>
+    <t>BusROCOF_22</t>
+  </si>
+  <si>
+    <t>BusROCOF 22</t>
+  </si>
+  <si>
+    <t>BusROCOF_23</t>
+  </si>
+  <si>
+    <t>BusROCOF 23</t>
+  </si>
+  <si>
+    <t>BusROCOF_24</t>
+  </si>
+  <si>
+    <t>BusROCOF 24</t>
+  </si>
+  <si>
+    <t>BusROCOF_25</t>
+  </si>
+  <si>
+    <t>BusROCOF 25</t>
+  </si>
+  <si>
+    <t>BusROCOF_26</t>
+  </si>
+  <si>
+    <t>BusROCOF 26</t>
+  </si>
+  <si>
+    <t>BusROCOF_27</t>
+  </si>
+  <si>
+    <t>BusROCOF 27</t>
+  </si>
+  <si>
+    <t>BusROCOF_28</t>
+  </si>
+  <si>
+    <t>BusROCOF 28</t>
+  </si>
+  <si>
+    <t>BusROCOF_29</t>
+  </si>
+  <si>
+    <t>BusROCOF 29</t>
+  </si>
+  <si>
+    <t>BusROCOF_30</t>
+  </si>
+  <si>
+    <t>BusROCOF 30</t>
+  </si>
+  <si>
+    <t>BusROCOF_31</t>
+  </si>
+  <si>
+    <t>BusROCOF 31</t>
+  </si>
+  <si>
+    <t>BusROCOF_32</t>
+  </si>
+  <si>
+    <t>BusROCOF 32</t>
+  </si>
+  <si>
+    <t>BusROCOF_33</t>
+  </si>
+  <si>
+    <t>BusROCOF 33</t>
+  </si>
+  <si>
+    <t>BusROCOF_34</t>
+  </si>
+  <si>
+    <t>BusROCOF 34</t>
+  </si>
+  <si>
+    <t>BusROCOF_35</t>
+  </si>
+  <si>
+    <t>BusROCOF 35</t>
+  </si>
+  <si>
+    <t>BusROCOF_36</t>
+  </si>
+  <si>
+    <t>BusROCOF 36</t>
+  </si>
+  <si>
+    <t>BusROCOF_37</t>
+  </si>
+  <si>
+    <t>BusROCOF 37</t>
+  </si>
+  <si>
+    <t>BusROCOF_38</t>
+  </si>
+  <si>
+    <t>BusROCOF 38</t>
+  </si>
+  <si>
+    <t>BusROCOF_39</t>
+  </si>
+  <si>
+    <t>BusROCOF 39</t>
+  </si>
+  <si>
+    <t>ug</t>
+  </si>
+  <si>
+    <t>Sg</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -888,25 +1165,6 @@
       <color rgb="FF000000"/>
       <name val="Courier New"/>
       <family val="3"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="18"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -930,7 +1188,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -967,51 +1225,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color rgb="FFFFFFFF"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFFFFFFF"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFFFFFFF"/>
-      </top>
-      <bottom style="thick">
-        <color rgb="FFFFFFFF"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFFFFFFF"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFFFFFFF"/>
-      </right>
-      <top style="thick">
-        <color rgb="FFFFFFFF"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FFFFFFFF"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFFFFFFF"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFFFFFFF"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFFFFFFF"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FFFFFFFF"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color auto="1"/>
       </left>
@@ -1026,7 +1239,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1044,22 +1257,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1369,46 +1574,46 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>12</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
@@ -1422,7 +1627,7 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="E2">
         <v>345</v>
@@ -1466,7 +1671,7 @@
         <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="E3">
         <v>345</v>
@@ -1510,7 +1715,7 @@
         <v>1</v>
       </c>
       <c r="D4" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="E4">
         <v>345</v>
@@ -1554,7 +1759,7 @@
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="E5">
         <v>345</v>
@@ -1598,7 +1803,7 @@
         <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="E6">
         <v>345</v>
@@ -1642,7 +1847,7 @@
         <v>1</v>
       </c>
       <c r="D7" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="E7">
         <v>345</v>
@@ -1686,7 +1891,7 @@
         <v>1</v>
       </c>
       <c r="D8" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="E8">
         <v>345</v>
@@ -1730,7 +1935,7 @@
         <v>1</v>
       </c>
       <c r="D9" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="E9">
         <v>345</v>
@@ -1774,7 +1979,7 @@
         <v>1</v>
       </c>
       <c r="D10" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="E10">
         <v>345</v>
@@ -1818,7 +2023,7 @@
         <v>1</v>
       </c>
       <c r="D11" t="s">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="E11">
         <v>345</v>
@@ -1862,7 +2067,7 @@
         <v>1</v>
       </c>
       <c r="D12" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="E12">
         <v>345</v>
@@ -1906,7 +2111,7 @@
         <v>1</v>
       </c>
       <c r="D13" t="s">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="E13">
         <v>138</v>
@@ -1950,7 +2155,7 @@
         <v>1</v>
       </c>
       <c r="D14" t="s">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="E14">
         <v>345</v>
@@ -1994,7 +2199,7 @@
         <v>1</v>
       </c>
       <c r="D15" t="s">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="E15">
         <v>345</v>
@@ -2038,7 +2243,7 @@
         <v>1</v>
       </c>
       <c r="D16" t="s">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="E16">
         <v>345</v>
@@ -2082,7 +2287,7 @@
         <v>1</v>
       </c>
       <c r="D17" t="s">
-        <v>29</v>
+        <v>51</v>
       </c>
       <c r="E17">
         <v>345</v>
@@ -2126,7 +2331,7 @@
         <v>1</v>
       </c>
       <c r="D18" t="s">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="E18">
         <v>345</v>
@@ -2170,7 +2375,7 @@
         <v>1</v>
       </c>
       <c r="D19" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="E19">
         <v>345</v>
@@ -2214,7 +2419,7 @@
         <v>1</v>
       </c>
       <c r="D20" t="s">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="E20">
         <v>345</v>
@@ -2258,7 +2463,7 @@
         <v>1</v>
       </c>
       <c r="D21" t="s">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="E21">
         <v>138</v>
@@ -2302,7 +2507,7 @@
         <v>1</v>
       </c>
       <c r="D22" t="s">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="E22">
         <v>345</v>
@@ -2346,7 +2551,7 @@
         <v>1</v>
       </c>
       <c r="D23" t="s">
-        <v>35</v>
+        <v>57</v>
       </c>
       <c r="E23">
         <v>345</v>
@@ -2390,7 +2595,7 @@
         <v>1</v>
       </c>
       <c r="D24" t="s">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="E24">
         <v>345</v>
@@ -2434,7 +2639,7 @@
         <v>1</v>
       </c>
       <c r="D25" t="s">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="E25">
         <v>345</v>
@@ -2478,7 +2683,7 @@
         <v>1</v>
       </c>
       <c r="D26" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="E26">
         <v>345</v>
@@ -2522,7 +2727,7 @@
         <v>1</v>
       </c>
       <c r="D27" t="s">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="E27">
         <v>345</v>
@@ -2566,7 +2771,7 @@
         <v>1</v>
       </c>
       <c r="D28" t="s">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="E28">
         <v>345</v>
@@ -2610,7 +2815,7 @@
         <v>1</v>
       </c>
       <c r="D29" t="s">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="E29">
         <v>345</v>
@@ -2654,7 +2859,7 @@
         <v>1</v>
       </c>
       <c r="D30" t="s">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="E30">
         <v>345</v>
@@ -2698,7 +2903,7 @@
         <v>1</v>
       </c>
       <c r="D31" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="E31">
         <v>34.5</v>
@@ -2742,7 +2947,7 @@
         <v>1</v>
       </c>
       <c r="D32" t="s">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="E32">
         <v>34.5</v>
@@ -2786,7 +2991,7 @@
         <v>1</v>
       </c>
       <c r="D33" t="s">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="E33">
         <v>21</v>
@@ -2830,7 +3035,7 @@
         <v>1</v>
       </c>
       <c r="D34" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="E34">
         <v>21</v>
@@ -2874,7 +3079,7 @@
         <v>1</v>
       </c>
       <c r="D35" t="s">
-        <v>47</v>
+        <v>69</v>
       </c>
       <c r="E35">
         <v>15.5</v>
@@ -2918,7 +3123,7 @@
         <v>1</v>
       </c>
       <c r="D36" t="s">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="E36">
         <v>15.5</v>
@@ -2962,7 +3167,7 @@
         <v>1</v>
       </c>
       <c r="D37" t="s">
-        <v>49</v>
+        <v>71</v>
       </c>
       <c r="E37">
         <v>12.5</v>
@@ -3006,7 +3211,7 @@
         <v>1</v>
       </c>
       <c r="D38" t="s">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="E38">
         <v>12.5</v>
@@ -3050,7 +3255,7 @@
         <v>1</v>
       </c>
       <c r="D39" t="s">
-        <v>51</v>
+        <v>73</v>
       </c>
       <c r="E39">
         <v>34.5</v>
@@ -3094,7 +3299,7 @@
         <v>1</v>
       </c>
       <c r="D40" t="s">
-        <v>52</v>
+        <v>74</v>
       </c>
       <c r="E40">
         <v>345</v>
@@ -3133,52 +3338,52 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
         <v>13</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
@@ -3186,16 +3391,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>184</v>
+        <v>14</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>184</v>
+        <v>14</v>
       </c>
       <c r="E2" t="s">
-        <v>168</v>
+        <v>15</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -3207,7 +3412,7 @@
         <v>1.05</v>
       </c>
       <c r="J2">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="K2">
         <v>0.05</v>
@@ -3227,16 +3432,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>185</v>
+        <v>16</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>185</v>
+        <v>16</v>
       </c>
       <c r="E3" t="s">
-        <v>169</v>
+        <v>17</v>
       </c>
       <c r="G3">
         <v>1</v>
@@ -3248,7 +3453,7 @@
         <v>1.05</v>
       </c>
       <c r="J3">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="K3">
         <v>0.05</v>
@@ -3268,16 +3473,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>186</v>
+        <v>18</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
       <c r="D4" t="s">
-        <v>186</v>
+        <v>18</v>
       </c>
       <c r="E4" t="s">
-        <v>170</v>
+        <v>19</v>
       </c>
       <c r="G4">
         <v>1</v>
@@ -3289,7 +3494,7 @@
         <v>1.05</v>
       </c>
       <c r="J4">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="K4">
         <v>0.05</v>
@@ -3309,16 +3514,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>187</v>
+        <v>20</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>187</v>
+        <v>20</v>
       </c>
       <c r="E5" t="s">
-        <v>171</v>
+        <v>21</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -3330,7 +3535,7 @@
         <v>1.05</v>
       </c>
       <c r="J5">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="K5">
         <v>0.05</v>
@@ -3350,16 +3555,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>188</v>
+        <v>22</v>
       </c>
       <c r="C6">
         <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>188</v>
+        <v>22</v>
       </c>
       <c r="E6" t="s">
-        <v>172</v>
+        <v>23</v>
       </c>
       <c r="G6">
         <v>1</v>
@@ -3371,7 +3576,7 @@
         <v>1.05</v>
       </c>
       <c r="J6">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="K6">
         <v>0.05</v>
@@ -3391,16 +3596,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>189</v>
+        <v>24</v>
       </c>
       <c r="C7">
         <v>1</v>
       </c>
       <c r="D7" t="s">
-        <v>189</v>
+        <v>24</v>
       </c>
       <c r="E7" t="s">
-        <v>173</v>
+        <v>25</v>
       </c>
       <c r="G7">
         <v>1</v>
@@ -3412,7 +3617,7 @@
         <v>1.05</v>
       </c>
       <c r="J7">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="K7">
         <v>0.05</v>
@@ -3433,7 +3638,1072 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
+  <dimension ref="A1:Q7"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>365</v>
+      </c>
+      <c r="P1" t="s">
+        <v>366</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>0.05</v>
+      </c>
+      <c r="I2">
+        <v>1.05</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>0.05</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+      <c r="M2">
+        <v>2.1</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2">
+        <v>1</v>
+      </c>
+      <c r="P2">
+        <v>836</v>
+      </c>
+      <c r="Q2">
+        <v>34.5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>0.05</v>
+      </c>
+      <c r="I3">
+        <v>1.05</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>0.05</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
+      </c>
+      <c r="M3">
+        <v>2.1</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <v>1</v>
+      </c>
+      <c r="P3">
+        <v>843.7</v>
+      </c>
+      <c r="Q3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>0.05</v>
+      </c>
+      <c r="I4">
+        <v>1.05</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>0.05</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>2.1</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <v>1</v>
+      </c>
+      <c r="P4">
+        <v>1174.8</v>
+      </c>
+      <c r="Q4">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" t="s">
+        <v>21</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>0.05</v>
+      </c>
+      <c r="I5">
+        <v>1.05</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>0.05</v>
+      </c>
+      <c r="L5">
+        <v>1</v>
+      </c>
+      <c r="M5">
+        <v>2.1</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>1</v>
+      </c>
+      <c r="P5">
+        <v>1080.2</v>
+      </c>
+      <c r="Q5">
+        <v>15.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" t="s">
+        <v>23</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>0.05</v>
+      </c>
+      <c r="I6">
+        <v>1.05</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>0.05</v>
+      </c>
+      <c r="L6">
+        <v>1</v>
+      </c>
+      <c r="M6">
+        <v>2.1</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <v>1</v>
+      </c>
+      <c r="P6">
+        <v>1025.2</v>
+      </c>
+      <c r="Q6">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" t="s">
+        <v>25</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>0.05</v>
+      </c>
+      <c r="I7">
+        <v>1.05</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>0.05</v>
+      </c>
+      <c r="L7">
+        <v>1</v>
+      </c>
+      <c r="M7">
+        <v>2.1</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>1</v>
+      </c>
+      <c r="P7">
+        <v>1199</v>
+      </c>
+      <c r="Q7">
+        <v>345</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
+  <dimension ref="A1:U11"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1" t="s">
+        <v>12</v>
+      </c>
+      <c r="K1" t="s">
+        <v>211</v>
+      </c>
+      <c r="L1" t="s">
+        <v>212</v>
+      </c>
+      <c r="M1" t="s">
+        <v>213</v>
+      </c>
+      <c r="N1" t="s">
+        <v>214</v>
+      </c>
+      <c r="O1" t="s">
+        <v>215</v>
+      </c>
+      <c r="P1" t="s">
+        <v>216</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>217</v>
+      </c>
+      <c r="R1" t="s">
+        <v>218</v>
+      </c>
+      <c r="S1" t="s">
+        <v>365</v>
+      </c>
+      <c r="T1" t="s">
+        <v>366</v>
+      </c>
+      <c r="U1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>219</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2" t="s">
+        <v>219</v>
+      </c>
+      <c r="E2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="Q2">
+        <v>6.5</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>1</v>
+      </c>
+      <c r="T2">
+        <v>836</v>
+      </c>
+      <c r="U2">
+        <v>34.5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>220</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3" t="s">
+        <v>220</v>
+      </c>
+      <c r="E3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="Q3">
+        <v>7.5</v>
+      </c>
+      <c r="R3">
+        <v>0</v>
+      </c>
+      <c r="S3">
+        <v>1</v>
+      </c>
+      <c r="T3">
+        <v>843.7</v>
+      </c>
+      <c r="U3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>221</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4" t="s">
+        <v>221</v>
+      </c>
+      <c r="E4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="Q4">
+        <v>6.82</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>1</v>
+      </c>
+      <c r="T4">
+        <v>1174.8</v>
+      </c>
+      <c r="U4">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>222</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5" t="s">
+        <v>222</v>
+      </c>
+      <c r="E5" t="s">
+        <v>21</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="Q5">
+        <v>5.5</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>1</v>
+      </c>
+      <c r="T5">
+        <v>1080.2</v>
+      </c>
+      <c r="U5">
+        <v>15.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>223</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6" t="s">
+        <v>223</v>
+      </c>
+      <c r="E6" t="s">
+        <v>23</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="Q6">
+        <v>5.95</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>1</v>
+      </c>
+      <c r="T6">
+        <v>1025.2</v>
+      </c>
+      <c r="U6">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>224</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7" t="s">
+        <v>224</v>
+      </c>
+      <c r="E7" t="s">
+        <v>25</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="Q7">
+        <v>11</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>1</v>
+      </c>
+      <c r="T7">
+        <v>1199</v>
+      </c>
+      <c r="U7">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="Q9" s="10"/>
+      <c r="R9" s="10"/>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="Q10" s="10"/>
+      <c r="R10" s="10"/>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="Q11" s="10"/>
+      <c r="R11" s="10"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
+  <dimension ref="A1:S7"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>225</v>
+      </c>
+      <c r="L1" t="s">
+        <v>226</v>
+      </c>
+      <c r="M1" t="s">
+        <v>10</v>
+      </c>
+      <c r="N1" t="s">
+        <v>11</v>
+      </c>
+      <c r="O1" t="s">
+        <v>12</v>
+      </c>
+      <c r="P1" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>365</v>
+      </c>
+      <c r="R1" t="s">
+        <v>366</v>
+      </c>
+      <c r="S1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>227</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2" t="s">
+        <v>227</v>
+      </c>
+      <c r="E2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>0.05</v>
+      </c>
+      <c r="I2">
+        <v>1.05</v>
+      </c>
+      <c r="J2">
+        <v>0.1</v>
+      </c>
+      <c r="K2">
+        <v>5</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+      <c r="M2">
+        <v>0.05</v>
+      </c>
+      <c r="N2">
+        <v>1</v>
+      </c>
+      <c r="O2">
+        <v>2.1</v>
+      </c>
+      <c r="P2">
+        <v>0</v>
+      </c>
+      <c r="Q2">
+        <v>1</v>
+      </c>
+      <c r="R2">
+        <v>836</v>
+      </c>
+      <c r="S2">
+        <v>34.5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>228</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3" t="s">
+        <v>228</v>
+      </c>
+      <c r="E3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>0.05</v>
+      </c>
+      <c r="I3">
+        <v>1.05</v>
+      </c>
+      <c r="J3">
+        <v>0.1</v>
+      </c>
+      <c r="K3">
+        <v>5</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
+      </c>
+      <c r="M3">
+        <v>0.05</v>
+      </c>
+      <c r="N3">
+        <v>1</v>
+      </c>
+      <c r="O3">
+        <v>2.1</v>
+      </c>
+      <c r="P3">
+        <v>0</v>
+      </c>
+      <c r="Q3">
+        <v>1</v>
+      </c>
+      <c r="R3">
+        <v>843.7</v>
+      </c>
+      <c r="S3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>229</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4" t="s">
+        <v>229</v>
+      </c>
+      <c r="E4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>0.05</v>
+      </c>
+      <c r="I4">
+        <v>1.05</v>
+      </c>
+      <c r="J4">
+        <v>0.1</v>
+      </c>
+      <c r="K4">
+        <v>5</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>0.05</v>
+      </c>
+      <c r="N4">
+        <v>1</v>
+      </c>
+      <c r="O4">
+        <v>2.1</v>
+      </c>
+      <c r="P4">
+        <v>0</v>
+      </c>
+      <c r="Q4">
+        <v>1</v>
+      </c>
+      <c r="R4">
+        <v>1174.8</v>
+      </c>
+      <c r="S4">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>230</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5" t="s">
+        <v>230</v>
+      </c>
+      <c r="E5" t="s">
+        <v>21</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>0.05</v>
+      </c>
+      <c r="I5">
+        <v>1.05</v>
+      </c>
+      <c r="J5">
+        <v>0.1</v>
+      </c>
+      <c r="K5">
+        <v>5</v>
+      </c>
+      <c r="L5">
+        <v>1</v>
+      </c>
+      <c r="M5">
+        <v>0.05</v>
+      </c>
+      <c r="N5">
+        <v>1</v>
+      </c>
+      <c r="O5">
+        <v>2.1</v>
+      </c>
+      <c r="P5">
+        <v>0</v>
+      </c>
+      <c r="Q5">
+        <v>1</v>
+      </c>
+      <c r="R5">
+        <v>1080.2</v>
+      </c>
+      <c r="S5">
+        <v>15.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>231</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6" t="s">
+        <v>231</v>
+      </c>
+      <c r="E6" t="s">
+        <v>23</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>0.05</v>
+      </c>
+      <c r="I6">
+        <v>1.05</v>
+      </c>
+      <c r="J6">
+        <v>0.1</v>
+      </c>
+      <c r="K6">
+        <v>5</v>
+      </c>
+      <c r="L6">
+        <v>1</v>
+      </c>
+      <c r="M6">
+        <v>0.05</v>
+      </c>
+      <c r="N6">
+        <v>1</v>
+      </c>
+      <c r="O6">
+        <v>2.1</v>
+      </c>
+      <c r="P6">
+        <v>0</v>
+      </c>
+      <c r="Q6">
+        <v>1</v>
+      </c>
+      <c r="R6">
+        <v>1025.2</v>
+      </c>
+      <c r="S6">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>232</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7" t="s">
+        <v>232</v>
+      </c>
+      <c r="E7" t="s">
+        <v>25</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>0.05</v>
+      </c>
+      <c r="I7">
+        <v>1.05</v>
+      </c>
+      <c r="J7">
+        <v>0.1</v>
+      </c>
+      <c r="K7">
+        <v>5</v>
+      </c>
+      <c r="L7">
+        <v>1</v>
+      </c>
+      <c r="M7">
+        <v>0.05</v>
+      </c>
+      <c r="N7">
+        <v>1</v>
+      </c>
+      <c r="O7">
+        <v>2.1</v>
+      </c>
+      <c r="P7">
+        <v>0</v>
+      </c>
+      <c r="Q7">
+        <v>1</v>
+      </c>
+      <c r="R7">
+        <v>1199</v>
+      </c>
+      <c r="S7">
+        <v>345</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:T7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
@@ -3442,64 +4712,64 @@
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>174</v>
+        <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>190</v>
+        <v>233</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>191</v>
+        <v>234</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>192</v>
+        <v>235</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>193</v>
+        <v>236</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>194</v>
+        <v>237</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>195</v>
+        <v>238</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>196</v>
+        <v>239</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>197</v>
+        <v>240</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>198</v>
+        <v>241</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>199</v>
+        <v>242</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>200</v>
+        <v>243</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>201</v>
+        <v>244</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>202</v>
+        <v>245</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>203</v>
+        <v>246</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>204</v>
+        <v>247</v>
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.2">
@@ -3507,16 +4777,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>205</v>
+        <v>248</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2" t="s">
-        <v>205</v>
+        <v>248</v>
       </c>
       <c r="E2" t="s">
-        <v>168</v>
+        <v>15</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -3569,16 +4839,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>206</v>
+        <v>249</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3" t="s">
-        <v>206</v>
+        <v>249</v>
       </c>
       <c r="E3" t="s">
-        <v>169</v>
+        <v>17</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -3631,16 +4901,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>207</v>
+        <v>250</v>
       </c>
       <c r="C4">
         <v>0</v>
       </c>
       <c r="D4" t="s">
-        <v>207</v>
+        <v>250</v>
       </c>
       <c r="E4" t="s">
-        <v>170</v>
+        <v>19</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -3693,16 +4963,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>208</v>
+        <v>251</v>
       </c>
       <c r="C5">
         <v>0</v>
       </c>
       <c r="D5" t="s">
-        <v>208</v>
+        <v>251</v>
       </c>
       <c r="E5" t="s">
-        <v>171</v>
+        <v>21</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -3755,16 +5025,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>209</v>
+        <v>252</v>
       </c>
       <c r="C6">
         <v>0</v>
       </c>
       <c r="D6" t="s">
-        <v>209</v>
+        <v>252</v>
       </c>
       <c r="E6" t="s">
-        <v>172</v>
+        <v>23</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -3817,16 +5087,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>210</v>
+        <v>253</v>
       </c>
       <c r="C7">
         <v>0</v>
       </c>
       <c r="D7" t="s">
-        <v>210</v>
+        <v>253</v>
       </c>
       <c r="E7" t="s">
-        <v>173</v>
+        <v>25</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -3879,86 +5149,86 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="A1:Y7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="R1" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="H1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>222</v>
-      </c>
       <c r="U1" s="1" t="s">
-        <v>223</v>
+        <v>263</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>224</v>
+        <v>264</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>225</v>
+        <v>265</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>226</v>
+        <v>266</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>227</v>
+        <v>267</v>
       </c>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.2">
@@ -3966,22 +5236,22 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>228</v>
+        <v>268</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2" t="s">
-        <v>228</v>
+        <v>268</v>
       </c>
       <c r="E2" t="s">
-        <v>205</v>
+        <v>248</v>
       </c>
       <c r="F2">
         <v>3</v>
       </c>
       <c r="H2" t="s">
-        <v>235</v>
+        <v>269</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -4040,22 +5310,22 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>229</v>
+        <v>270</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3" t="s">
-        <v>229</v>
+        <v>270</v>
       </c>
       <c r="E3" t="s">
-        <v>206</v>
+        <v>249</v>
       </c>
       <c r="F3">
         <v>3</v>
       </c>
       <c r="H3" t="s">
-        <v>236</v>
+        <v>271</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -4114,22 +5384,22 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>230</v>
+        <v>272</v>
       </c>
       <c r="C4">
         <v>0</v>
       </c>
       <c r="D4" t="s">
-        <v>230</v>
+        <v>272</v>
       </c>
       <c r="E4" t="s">
-        <v>207</v>
+        <v>250</v>
       </c>
       <c r="F4">
         <v>3</v>
       </c>
       <c r="H4" t="s">
-        <v>237</v>
+        <v>273</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -4188,22 +5458,22 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>231</v>
+        <v>274</v>
       </c>
       <c r="C5">
         <v>0</v>
       </c>
       <c r="D5" t="s">
-        <v>231</v>
+        <v>274</v>
       </c>
       <c r="E5" t="s">
-        <v>208</v>
+        <v>251</v>
       </c>
       <c r="F5">
         <v>3</v>
       </c>
       <c r="H5" t="s">
-        <v>238</v>
+        <v>275</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4262,22 +5532,22 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>232</v>
+        <v>276</v>
       </c>
       <c r="C6">
         <v>0</v>
       </c>
       <c r="D6" t="s">
-        <v>232</v>
+        <v>276</v>
       </c>
       <c r="E6" t="s">
-        <v>209</v>
+        <v>252</v>
       </c>
       <c r="F6">
         <v>3</v>
       </c>
       <c r="H6" t="s">
-        <v>240</v>
+        <v>277</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4336,22 +5606,22 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>233</v>
+        <v>278</v>
       </c>
       <c r="C7">
         <v>0</v>
       </c>
       <c r="D7" t="s">
-        <v>233</v>
+        <v>278</v>
       </c>
       <c r="E7" t="s">
-        <v>210</v>
+        <v>253</v>
       </c>
       <c r="F7">
         <v>3</v>
       </c>
       <c r="H7" t="s">
-        <v>243</v>
+        <v>279</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -4410,8 +5680,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
@@ -4420,28 +5690,28 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>244</v>
+        <v>280</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>245</v>
+        <v>281</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>85</v>
+        <v>107</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
@@ -4449,13 +5719,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>234</v>
+        <v>282</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>234</v>
+        <v>282</v>
       </c>
       <c r="E2">
         <v>30</v>
@@ -4475,13 +5745,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>235</v>
+        <v>269</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>235</v>
+        <v>269</v>
       </c>
       <c r="E3">
         <v>31</v>
@@ -4501,13 +5771,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>236</v>
+        <v>271</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
       <c r="D4" t="s">
-        <v>236</v>
+        <v>271</v>
       </c>
       <c r="E4">
         <v>32</v>
@@ -4527,13 +5797,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>237</v>
+        <v>273</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>237</v>
+        <v>273</v>
       </c>
       <c r="E5">
         <v>33</v>
@@ -4553,13 +5823,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>238</v>
+        <v>275</v>
       </c>
       <c r="C6">
         <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>238</v>
+        <v>275</v>
       </c>
       <c r="E6">
         <v>34</v>
@@ -4579,13 +5849,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>239</v>
+        <v>283</v>
       </c>
       <c r="C7">
         <v>1</v>
       </c>
       <c r="D7" t="s">
-        <v>239</v>
+        <v>283</v>
       </c>
       <c r="E7">
         <v>35</v>
@@ -4605,13 +5875,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>240</v>
+        <v>277</v>
       </c>
       <c r="C8">
         <v>1</v>
       </c>
       <c r="D8" t="s">
-        <v>240</v>
+        <v>277</v>
       </c>
       <c r="E8">
         <v>36</v>
@@ -4631,13 +5901,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>241</v>
+        <v>284</v>
       </c>
       <c r="C9">
         <v>1</v>
       </c>
       <c r="D9" t="s">
-        <v>241</v>
+        <v>284</v>
       </c>
       <c r="E9">
         <v>37</v>
@@ -4657,13 +5927,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>242</v>
+        <v>285</v>
       </c>
       <c r="C10">
         <v>1</v>
       </c>
       <c r="D10" t="s">
-        <v>242</v>
+        <v>285</v>
       </c>
       <c r="E10">
         <v>38</v>
@@ -4683,13 +5953,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>243</v>
+        <v>279</v>
       </c>
       <c r="C11">
         <v>1</v>
       </c>
       <c r="D11" t="s">
-        <v>243</v>
+        <v>279</v>
       </c>
       <c r="E11">
         <v>39</v>
@@ -4709,20 +5979,1070 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E15E4C19-FBCE-4B77-81F5-DD53FDE8EE36}">
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
+  <dimension ref="A1:H40"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>75</v>
+      </c>
+      <c r="F1" t="s">
+        <v>286</v>
+      </c>
+      <c r="G1" t="s">
+        <v>281</v>
+      </c>
+      <c r="H1" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>287</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
+        <v>288</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>0.02</v>
+      </c>
+      <c r="G2">
+        <v>0.1</v>
+      </c>
+      <c r="H2">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>289</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3" t="s">
+        <v>290</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>0.02</v>
+      </c>
+      <c r="G3">
+        <v>0.1</v>
+      </c>
+      <c r="H3">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>291</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4" t="s">
+        <v>292</v>
+      </c>
+      <c r="E4">
+        <v>3</v>
+      </c>
+      <c r="F4">
+        <v>0.02</v>
+      </c>
+      <c r="G4">
+        <v>0.1</v>
+      </c>
+      <c r="H4">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>293</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5" t="s">
+        <v>294</v>
+      </c>
+      <c r="E5">
+        <v>4</v>
+      </c>
+      <c r="F5">
+        <v>0.02</v>
+      </c>
+      <c r="G5">
+        <v>0.1</v>
+      </c>
+      <c r="H5">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>295</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6" t="s">
+        <v>296</v>
+      </c>
+      <c r="E6">
+        <v>5</v>
+      </c>
+      <c r="F6">
+        <v>0.02</v>
+      </c>
+      <c r="G6">
+        <v>0.1</v>
+      </c>
+      <c r="H6">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>297</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7" t="s">
+        <v>298</v>
+      </c>
+      <c r="E7">
+        <v>6</v>
+      </c>
+      <c r="F7">
+        <v>0.02</v>
+      </c>
+      <c r="G7">
+        <v>0.1</v>
+      </c>
+      <c r="H7">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>299</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8" t="s">
+        <v>300</v>
+      </c>
+      <c r="E8">
+        <v>7</v>
+      </c>
+      <c r="F8">
+        <v>0.02</v>
+      </c>
+      <c r="G8">
+        <v>0.1</v>
+      </c>
+      <c r="H8">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>301</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9" t="s">
+        <v>302</v>
+      </c>
+      <c r="E9">
+        <v>8</v>
+      </c>
+      <c r="F9">
+        <v>0.02</v>
+      </c>
+      <c r="G9">
+        <v>0.1</v>
+      </c>
+      <c r="H9">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>303</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10" t="s">
+        <v>304</v>
+      </c>
+      <c r="E10">
+        <v>9</v>
+      </c>
+      <c r="F10">
+        <v>0.02</v>
+      </c>
+      <c r="G10">
+        <v>0.1</v>
+      </c>
+      <c r="H10">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>305</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11" t="s">
+        <v>306</v>
+      </c>
+      <c r="E11">
+        <v>10</v>
+      </c>
+      <c r="F11">
+        <v>0.02</v>
+      </c>
+      <c r="G11">
+        <v>0.1</v>
+      </c>
+      <c r="H11">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>307</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12" t="s">
+        <v>308</v>
+      </c>
+      <c r="E12">
+        <v>11</v>
+      </c>
+      <c r="F12">
+        <v>0.02</v>
+      </c>
+      <c r="G12">
+        <v>0.1</v>
+      </c>
+      <c r="H12">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>309</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13" t="s">
+        <v>310</v>
+      </c>
+      <c r="E13">
+        <v>12</v>
+      </c>
+      <c r="F13">
+        <v>0.02</v>
+      </c>
+      <c r="G13">
+        <v>0.1</v>
+      </c>
+      <c r="H13">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>311</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14" t="s">
+        <v>312</v>
+      </c>
+      <c r="E14">
+        <v>13</v>
+      </c>
+      <c r="F14">
+        <v>0.02</v>
+      </c>
+      <c r="G14">
+        <v>0.1</v>
+      </c>
+      <c r="H14">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>313</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15" t="s">
+        <v>314</v>
+      </c>
+      <c r="E15">
+        <v>14</v>
+      </c>
+      <c r="F15">
+        <v>0.02</v>
+      </c>
+      <c r="G15">
+        <v>0.1</v>
+      </c>
+      <c r="H15">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>315</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+      <c r="D16" t="s">
+        <v>316</v>
+      </c>
+      <c r="E16">
+        <v>15</v>
+      </c>
+      <c r="F16">
+        <v>0.02</v>
+      </c>
+      <c r="G16">
+        <v>0.1</v>
+      </c>
+      <c r="H16">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>317</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17" t="s">
+        <v>318</v>
+      </c>
+      <c r="E17">
+        <v>16</v>
+      </c>
+      <c r="F17">
+        <v>0.02</v>
+      </c>
+      <c r="G17">
+        <v>0.1</v>
+      </c>
+      <c r="H17">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>319</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18" t="s">
+        <v>320</v>
+      </c>
+      <c r="E18">
+        <v>17</v>
+      </c>
+      <c r="F18">
+        <v>0.02</v>
+      </c>
+      <c r="G18">
+        <v>0.1</v>
+      </c>
+      <c r="H18">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>321</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+      <c r="D19" t="s">
+        <v>322</v>
+      </c>
+      <c r="E19">
+        <v>18</v>
+      </c>
+      <c r="F19">
+        <v>0.02</v>
+      </c>
+      <c r="G19">
+        <v>0.1</v>
+      </c>
+      <c r="H19">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>323</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20" t="s">
+        <v>324</v>
+      </c>
+      <c r="E20">
+        <v>19</v>
+      </c>
+      <c r="F20">
+        <v>0.02</v>
+      </c>
+      <c r="G20">
+        <v>0.1</v>
+      </c>
+      <c r="H20">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>325</v>
+      </c>
+      <c r="C21">
+        <v>1</v>
+      </c>
+      <c r="D21" t="s">
+        <v>326</v>
+      </c>
+      <c r="E21">
+        <v>20</v>
+      </c>
+      <c r="F21">
+        <v>0.02</v>
+      </c>
+      <c r="G21">
+        <v>0.1</v>
+      </c>
+      <c r="H21">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>327</v>
+      </c>
+      <c r="C22">
+        <v>1</v>
+      </c>
+      <c r="D22" t="s">
+        <v>328</v>
+      </c>
+      <c r="E22">
+        <v>21</v>
+      </c>
+      <c r="F22">
+        <v>0.02</v>
+      </c>
+      <c r="G22">
+        <v>0.1</v>
+      </c>
+      <c r="H22">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>329</v>
+      </c>
+      <c r="C23">
+        <v>1</v>
+      </c>
+      <c r="D23" t="s">
+        <v>330</v>
+      </c>
+      <c r="E23">
+        <v>22</v>
+      </c>
+      <c r="F23">
+        <v>0.02</v>
+      </c>
+      <c r="G23">
+        <v>0.1</v>
+      </c>
+      <c r="H23">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>331</v>
+      </c>
+      <c r="C24">
+        <v>1</v>
+      </c>
+      <c r="D24" t="s">
+        <v>332</v>
+      </c>
+      <c r="E24">
+        <v>23</v>
+      </c>
+      <c r="F24">
+        <v>0.02</v>
+      </c>
+      <c r="G24">
+        <v>0.1</v>
+      </c>
+      <c r="H24">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>333</v>
+      </c>
+      <c r="C25">
+        <v>1</v>
+      </c>
+      <c r="D25" t="s">
+        <v>334</v>
+      </c>
+      <c r="E25">
+        <v>24</v>
+      </c>
+      <c r="F25">
+        <v>0.02</v>
+      </c>
+      <c r="G25">
+        <v>0.1</v>
+      </c>
+      <c r="H25">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>335</v>
+      </c>
+      <c r="C26">
+        <v>1</v>
+      </c>
+      <c r="D26" t="s">
+        <v>336</v>
+      </c>
+      <c r="E26">
+        <v>25</v>
+      </c>
+      <c r="F26">
+        <v>0.02</v>
+      </c>
+      <c r="G26">
+        <v>0.1</v>
+      </c>
+      <c r="H26">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>337</v>
+      </c>
+      <c r="C27">
+        <v>1</v>
+      </c>
+      <c r="D27" t="s">
+        <v>338</v>
+      </c>
+      <c r="E27">
+        <v>26</v>
+      </c>
+      <c r="F27">
+        <v>0.02</v>
+      </c>
+      <c r="G27">
+        <v>0.1</v>
+      </c>
+      <c r="H27">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
+        <v>339</v>
+      </c>
+      <c r="C28">
+        <v>1</v>
+      </c>
+      <c r="D28" t="s">
+        <v>340</v>
+      </c>
+      <c r="E28">
+        <v>27</v>
+      </c>
+      <c r="F28">
+        <v>0.02</v>
+      </c>
+      <c r="G28">
+        <v>0.1</v>
+      </c>
+      <c r="H28">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>341</v>
+      </c>
+      <c r="C29">
+        <v>1</v>
+      </c>
+      <c r="D29" t="s">
+        <v>342</v>
+      </c>
+      <c r="E29">
+        <v>28</v>
+      </c>
+      <c r="F29">
+        <v>0.02</v>
+      </c>
+      <c r="G29">
+        <v>0.1</v>
+      </c>
+      <c r="H29">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" t="s">
+        <v>343</v>
+      </c>
+      <c r="C30">
+        <v>1</v>
+      </c>
+      <c r="D30" t="s">
+        <v>344</v>
+      </c>
+      <c r="E30">
+        <v>29</v>
+      </c>
+      <c r="F30">
+        <v>0.02</v>
+      </c>
+      <c r="G30">
+        <v>0.1</v>
+      </c>
+      <c r="H30">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" t="s">
+        <v>345</v>
+      </c>
+      <c r="C31">
+        <v>1</v>
+      </c>
+      <c r="D31" t="s">
+        <v>346</v>
+      </c>
+      <c r="E31">
+        <v>30</v>
+      </c>
+      <c r="F31">
+        <v>0.02</v>
+      </c>
+      <c r="G31">
+        <v>0.1</v>
+      </c>
+      <c r="H31">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" t="s">
+        <v>347</v>
+      </c>
+      <c r="C32">
+        <v>1</v>
+      </c>
+      <c r="D32" t="s">
+        <v>348</v>
+      </c>
+      <c r="E32">
+        <v>31</v>
+      </c>
+      <c r="F32">
+        <v>0.02</v>
+      </c>
+      <c r="G32">
+        <v>0.1</v>
+      </c>
+      <c r="H32">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33" t="s">
+        <v>349</v>
+      </c>
+      <c r="C33">
+        <v>1</v>
+      </c>
+      <c r="D33" t="s">
+        <v>350</v>
+      </c>
+      <c r="E33">
+        <v>32</v>
+      </c>
+      <c r="F33">
+        <v>0.02</v>
+      </c>
+      <c r="G33">
+        <v>0.1</v>
+      </c>
+      <c r="H33">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34" t="s">
+        <v>351</v>
+      </c>
+      <c r="C34">
+        <v>1</v>
+      </c>
+      <c r="D34" t="s">
+        <v>352</v>
+      </c>
+      <c r="E34">
+        <v>33</v>
+      </c>
+      <c r="F34">
+        <v>0.02</v>
+      </c>
+      <c r="G34">
+        <v>0.1</v>
+      </c>
+      <c r="H34">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35" t="s">
+        <v>353</v>
+      </c>
+      <c r="C35">
+        <v>1</v>
+      </c>
+      <c r="D35" t="s">
+        <v>354</v>
+      </c>
+      <c r="E35">
+        <v>34</v>
+      </c>
+      <c r="F35">
+        <v>0.02</v>
+      </c>
+      <c r="G35">
+        <v>0.1</v>
+      </c>
+      <c r="H35">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36" t="s">
+        <v>355</v>
+      </c>
+      <c r="C36">
+        <v>1</v>
+      </c>
+      <c r="D36" t="s">
+        <v>356</v>
+      </c>
+      <c r="E36">
+        <v>35</v>
+      </c>
+      <c r="F36">
+        <v>0.02</v>
+      </c>
+      <c r="G36">
+        <v>0.1</v>
+      </c>
+      <c r="H36">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37" t="s">
+        <v>357</v>
+      </c>
+      <c r="C37">
+        <v>1</v>
+      </c>
+      <c r="D37" t="s">
+        <v>358</v>
+      </c>
+      <c r="E37">
+        <v>36</v>
+      </c>
+      <c r="F37">
+        <v>0.02</v>
+      </c>
+      <c r="G37">
+        <v>0.1</v>
+      </c>
+      <c r="H37">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38" t="s">
+        <v>359</v>
+      </c>
+      <c r="C38">
+        <v>1</v>
+      </c>
+      <c r="D38" t="s">
+        <v>360</v>
+      </c>
+      <c r="E38">
+        <v>37</v>
+      </c>
+      <c r="F38">
+        <v>0.02</v>
+      </c>
+      <c r="G38">
+        <v>0.1</v>
+      </c>
+      <c r="H38">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39" t="s">
+        <v>361</v>
+      </c>
+      <c r="C39">
+        <v>1</v>
+      </c>
+      <c r="D39" t="s">
+        <v>362</v>
+      </c>
+      <c r="E39">
+        <v>38</v>
+      </c>
+      <c r="F39">
+        <v>0.02</v>
+      </c>
+      <c r="G39">
+        <v>0.1</v>
+      </c>
+      <c r="H39">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40" t="s">
+        <v>363</v>
+      </c>
+      <c r="C40">
+        <v>1</v>
+      </c>
+      <c r="D40" t="s">
+        <v>364</v>
+      </c>
+      <c r="E40">
+        <v>39</v>
+      </c>
+      <c r="F40">
+        <v>0.02</v>
+      </c>
+      <c r="G40">
+        <v>0.1</v>
+      </c>
+      <c r="H40">
+        <v>0.02</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
   <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
@@ -4731,69 +7051,13 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>268</v>
+        <v>196</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>268</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4777E0E0-7471-47D8-8165-DDE9FB38FB92}">
-  <dimension ref="A1:G2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A2" s="1">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
-        <v>249</v>
-      </c>
-      <c r="C2">
-        <v>0</v>
-      </c>
-      <c r="D2" t="s">
-        <v>249</v>
-      </c>
-      <c r="E2" t="s">
-        <v>250</v>
-      </c>
-      <c r="F2" t="s">
-        <v>173</v>
-      </c>
-      <c r="G2">
-        <v>12</v>
+        <v>196</v>
       </c>
     </row>
   </sheetData>
@@ -4808,37 +7072,37 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>55</v>
+        <v>77</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>12</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
@@ -4846,13 +7110,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="E2">
         <v>3</v>
@@ -4881,13 +7145,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="E3">
         <v>4</v>
@@ -4916,13 +7180,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
       <c r="D4" t="s">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="E4">
         <v>7</v>
@@ -4951,13 +7215,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="E5">
         <v>8</v>
@@ -4986,13 +7250,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="C6">
         <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="E6">
         <v>12</v>
@@ -5021,13 +7285,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>61</v>
+        <v>83</v>
       </c>
       <c r="C7">
         <v>1</v>
       </c>
       <c r="D7" t="s">
-        <v>61</v>
+        <v>83</v>
       </c>
       <c r="E7">
         <v>15</v>
@@ -5056,13 +7320,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>62</v>
+        <v>84</v>
       </c>
       <c r="C8">
         <v>1</v>
       </c>
       <c r="D8" t="s">
-        <v>62</v>
+        <v>84</v>
       </c>
       <c r="E8">
         <v>16</v>
@@ -5074,7 +7338,7 @@
         <v>3.29</v>
       </c>
       <c r="H8">
-        <v>0.32299999999999995</v>
+        <v>0.32300000000000001</v>
       </c>
       <c r="I8">
         <v>1.2</v>
@@ -5091,13 +7355,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>63</v>
+        <v>85</v>
       </c>
       <c r="C9">
         <v>1</v>
       </c>
       <c r="D9" t="s">
-        <v>63</v>
+        <v>85</v>
       </c>
       <c r="E9">
         <v>18</v>
@@ -5126,13 +7390,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>64</v>
+        <v>86</v>
       </c>
       <c r="C10">
         <v>1</v>
       </c>
       <c r="D10" t="s">
-        <v>64</v>
+        <v>86</v>
       </c>
       <c r="E10">
         <v>20</v>
@@ -5161,13 +7425,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>65</v>
+        <v>87</v>
       </c>
       <c r="C11">
         <v>1</v>
       </c>
       <c r="D11" t="s">
-        <v>65</v>
+        <v>87</v>
       </c>
       <c r="E11">
         <v>21</v>
@@ -5196,13 +7460,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>66</v>
+        <v>88</v>
       </c>
       <c r="C12">
         <v>1</v>
       </c>
       <c r="D12" t="s">
-        <v>66</v>
+        <v>88</v>
       </c>
       <c r="E12">
         <v>23</v>
@@ -5231,13 +7495,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>67</v>
+        <v>89</v>
       </c>
       <c r="C13">
         <v>1</v>
       </c>
       <c r="D13" t="s">
-        <v>67</v>
+        <v>89</v>
       </c>
       <c r="E13">
         <v>24</v>
@@ -5246,7 +7510,7 @@
         <v>345</v>
       </c>
       <c r="G13">
-        <v>3.0860000000000003</v>
+        <v>3.0859999999999999</v>
       </c>
       <c r="H13">
         <v>-0.92200000000000004</v>
@@ -5266,13 +7530,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>68</v>
+        <v>90</v>
       </c>
       <c r="C14">
         <v>1</v>
       </c>
       <c r="D14" t="s">
-        <v>68</v>
+        <v>90</v>
       </c>
       <c r="E14">
         <v>25</v>
@@ -5284,7 +7548,7 @@
         <v>2.2400000000000002</v>
       </c>
       <c r="H14">
-        <v>0.47200000000000003</v>
+        <v>0.47199999999999998</v>
       </c>
       <c r="I14">
         <v>1.2</v>
@@ -5301,13 +7565,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="C15">
         <v>1</v>
       </c>
       <c r="D15" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="E15">
         <v>26</v>
@@ -5336,13 +7600,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>70</v>
+        <v>92</v>
       </c>
       <c r="C16">
         <v>1</v>
       </c>
       <c r="D16" t="s">
-        <v>70</v>
+        <v>92</v>
       </c>
       <c r="E16">
         <v>27</v>
@@ -5371,13 +7635,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>71</v>
+        <v>93</v>
       </c>
       <c r="C17">
         <v>1</v>
       </c>
       <c r="D17" t="s">
-        <v>71</v>
+        <v>93</v>
       </c>
       <c r="E17">
         <v>28</v>
@@ -5406,13 +7670,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="C18">
         <v>1</v>
       </c>
       <c r="D18" t="s">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="E18">
         <v>29</v>
@@ -5424,7 +7688,7 @@
         <v>2.835</v>
       </c>
       <c r="H18">
-        <v>1.2690000000000001</v>
+        <v>1.2689999999999999</v>
       </c>
       <c r="I18">
         <v>1.2</v>
@@ -5441,13 +7705,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="C19">
         <v>1</v>
       </c>
       <c r="D19" t="s">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="E19">
         <v>31</v>
@@ -5476,13 +7740,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="C20">
         <v>1</v>
       </c>
       <c r="D20" t="s">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="E20">
         <v>39</v>
@@ -5507,7 +7771,6 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -5522,61 +7785,61 @@
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>53</v>
-      </c>
       <c r="H1" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="J1" s="1" t="s">
-        <v>55</v>
+        <v>77</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>82</v>
+        <v>104</v>
       </c>
     </row>
     <row r="2" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.2">
@@ -5602,7 +7865,7 @@
         <v>30</v>
       </c>
       <c r="I2" s="4">
-        <v>4.3608638500000003</v>
+        <v>3.6954715999999999</v>
       </c>
       <c r="J2" s="4">
         <v>1.4</v>
@@ -5658,7 +7921,7 @@
         <v>31</v>
       </c>
       <c r="I3">
-        <v>6.4599999800000001</v>
+        <v>6.2110666500000002</v>
       </c>
       <c r="J3">
         <v>3</v>
@@ -5714,7 +7977,7 @@
         <v>32</v>
       </c>
       <c r="I4">
-        <v>7.2499999800000001</v>
+        <v>7.5</v>
       </c>
       <c r="J4">
         <v>3</v>
@@ -5770,7 +8033,7 @@
         <v>33</v>
       </c>
       <c r="I5">
-        <v>6.5199999799999997</v>
+        <v>6.3</v>
       </c>
       <c r="J5">
         <v>1.5806</v>
@@ -5826,7 +8089,7 @@
         <v>34</v>
       </c>
       <c r="I6">
-        <v>5.0799999800000002</v>
+        <v>5.5</v>
       </c>
       <c r="J6">
         <v>1.5853999999999999</v>
@@ -5882,7 +8145,7 @@
         <v>35</v>
       </c>
       <c r="I7" s="4">
-        <v>6.8699999800000002</v>
+        <v>6</v>
       </c>
       <c r="J7" s="4">
         <v>2.5777000000000001</v>
@@ -5938,7 +8201,7 @@
         <v>36</v>
       </c>
       <c r="I8">
-        <v>5.7999999799999999</v>
+        <v>5.95</v>
       </c>
       <c r="J8">
         <v>0.78759999999999997</v>
@@ -5994,7 +8257,7 @@
         <v>37</v>
       </c>
       <c r="I9" s="4">
-        <v>3.2152133800000002</v>
+        <v>5.64</v>
       </c>
       <c r="J9" s="4">
         <v>0</v>
@@ -6050,7 +8313,7 @@
         <v>38</v>
       </c>
       <c r="I10" s="4">
-        <v>7.6478338099999998</v>
+        <v>8.65</v>
       </c>
       <c r="J10" s="4">
         <v>1.4279999999999999</v>
@@ -6145,7 +8408,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
@@ -6156,64 +8419,64 @@
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>53</v>
-      </c>
       <c r="H1" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="J1" s="1" t="s">
-        <v>55</v>
+        <v>77</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>7</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.2">
@@ -6239,7 +8502,7 @@
         <v>39</v>
       </c>
       <c r="I2">
-        <v>5.7416999999999998</v>
+        <v>3.1174599999999999</v>
       </c>
       <c r="J2">
         <v>0.56169999999999998</v>
@@ -6287,34 +8550,34 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>83</v>
+        <v>105</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>85</v>
+        <v>107</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
@@ -6322,13 +8585,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>86</v>
+        <v>108</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>86</v>
+        <v>108</v>
       </c>
       <c r="E2">
         <v>4</v>
@@ -6346,7 +8609,7 @@
         <v>1</v>
       </c>
       <c r="J2">
-        <v>60</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
@@ -6354,13 +8617,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>87</v>
+        <v>109</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>87</v>
+        <v>109</v>
       </c>
       <c r="E3">
         <v>5</v>
@@ -6378,7 +8641,7 @@
         <v>2</v>
       </c>
       <c r="J3">
-        <v>60</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -6393,85 +8656,85 @@
   <sheetData>
     <row r="1" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>88</v>
+        <v>110</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>89</v>
+        <v>111</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>90</v>
+        <v>112</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>91</v>
+        <v>113</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>92</v>
+        <v>114</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>93</v>
+        <v>115</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>83</v>
+        <v>105</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>94</v>
+        <v>116</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>95</v>
+        <v>117</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>96</v>
+        <v>118</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>97</v>
+        <v>119</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>98</v>
+        <v>120</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>99</v>
+        <v>121</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>100</v>
+        <v>122</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="Y1" s="12" t="s">
-        <v>269</v>
-      </c>
-      <c r="Z1" s="12" t="s">
-        <v>270</v>
-      </c>
-      <c r="AA1" s="12" t="s">
-        <v>271</v>
+        <v>32</v>
+      </c>
+      <c r="Y1" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="Z1" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="AA1" s="9" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.2">
@@ -6479,13 +8742,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>101</v>
+        <v>126</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>101</v>
+        <v>126</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -6538,7 +8801,7 @@
       <c r="U2">
         <v>0</v>
       </c>
-      <c r="Y2" s="11">
+      <c r="Y2" s="8">
         <v>600</v>
       </c>
       <c r="Z2">
@@ -6553,13 +8816,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>102</v>
+        <v>127</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>102</v>
+        <v>127</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -6612,7 +8875,7 @@
       <c r="U3">
         <v>0</v>
       </c>
-      <c r="Y3" s="11">
+      <c r="Y3" s="8">
         <v>1000</v>
       </c>
       <c r="Z3">
@@ -6627,13 +8890,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>103</v>
+        <v>128</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
       <c r="D4" t="s">
-        <v>103</v>
+        <v>128</v>
       </c>
       <c r="E4">
         <v>2</v>
@@ -6686,7 +8949,7 @@
       <c r="U4">
         <v>0</v>
       </c>
-      <c r="Y4" s="11">
+      <c r="Y4" s="8">
         <v>500</v>
       </c>
       <c r="Z4">
@@ -6701,13 +8964,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>104</v>
+        <v>129</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>104</v>
+        <v>129</v>
       </c>
       <c r="E5">
         <v>2</v>
@@ -6760,7 +9023,7 @@
       <c r="U5">
         <v>0</v>
       </c>
-      <c r="Y5" s="11">
+      <c r="Y5" s="8">
         <v>500</v>
       </c>
       <c r="Z5">
@@ -6775,13 +9038,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>105</v>
+        <v>130</v>
       </c>
       <c r="C6">
         <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>105</v>
+        <v>130</v>
       </c>
       <c r="E6">
         <v>3</v>
@@ -6834,7 +9097,7 @@
       <c r="U6">
         <v>0</v>
       </c>
-      <c r="Y6" s="11">
+      <c r="Y6" s="8">
         <v>900</v>
       </c>
       <c r="Z6">
@@ -6849,13 +9112,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>106</v>
+        <v>131</v>
       </c>
       <c r="C7">
         <v>1</v>
       </c>
       <c r="D7" t="s">
-        <v>106</v>
+        <v>131</v>
       </c>
       <c r="E7">
         <v>3</v>
@@ -6908,7 +9171,7 @@
       <c r="U7">
         <v>0</v>
       </c>
-      <c r="Y7" s="11">
+      <c r="Y7" s="8">
         <v>500</v>
       </c>
       <c r="Z7">
@@ -6923,13 +9186,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>107</v>
+        <v>132</v>
       </c>
       <c r="C8">
         <v>1</v>
       </c>
       <c r="D8" t="s">
-        <v>107</v>
+        <v>132</v>
       </c>
       <c r="E8">
         <v>4</v>
@@ -6982,7 +9245,7 @@
       <c r="U8">
         <v>0</v>
       </c>
-      <c r="Y8" s="11">
+      <c r="Y8" s="8">
         <v>500</v>
       </c>
       <c r="Z8">
@@ -6997,13 +9260,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>108</v>
+        <v>133</v>
       </c>
       <c r="C9">
         <v>1</v>
       </c>
       <c r="D9" t="s">
-        <v>108</v>
+        <v>133</v>
       </c>
       <c r="E9">
         <v>4</v>
@@ -7056,7 +9319,7 @@
       <c r="U9">
         <v>0</v>
       </c>
-      <c r="Y9" s="11">
+      <c r="Y9" s="8">
         <v>600</v>
       </c>
       <c r="Z9">
@@ -7071,13 +9334,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>109</v>
+        <v>134</v>
       </c>
       <c r="C10">
         <v>1</v>
       </c>
       <c r="D10" t="s">
-        <v>109</v>
+        <v>134</v>
       </c>
       <c r="E10">
         <v>5</v>
@@ -7130,7 +9393,7 @@
       <c r="U10">
         <v>0</v>
       </c>
-      <c r="Y10" s="11">
+      <c r="Y10" s="8">
         <v>500</v>
       </c>
       <c r="Z10">
@@ -7145,13 +9408,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>110</v>
+        <v>135</v>
       </c>
       <c r="C11">
         <v>1</v>
       </c>
       <c r="D11" t="s">
-        <v>110</v>
+        <v>135</v>
       </c>
       <c r="E11">
         <v>5</v>
@@ -7204,7 +9467,7 @@
       <c r="U11">
         <v>0</v>
       </c>
-      <c r="Y11" s="11">
+      <c r="Y11" s="8">
         <v>1200</v>
       </c>
       <c r="Z11">
@@ -7219,13 +9482,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>111</v>
+        <v>136</v>
       </c>
       <c r="C12">
         <v>1</v>
       </c>
       <c r="D12" t="s">
-        <v>111</v>
+        <v>136</v>
       </c>
       <c r="E12">
         <v>6</v>
@@ -7278,7 +9541,7 @@
       <c r="U12">
         <v>0</v>
       </c>
-      <c r="Y12" s="11">
+      <c r="Y12" s="8">
         <v>900</v>
       </c>
       <c r="Z12">
@@ -7293,13 +9556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>112</v>
+        <v>137</v>
       </c>
       <c r="C13">
         <v>1</v>
       </c>
       <c r="D13" t="s">
-        <v>112</v>
+        <v>137</v>
       </c>
       <c r="E13">
         <v>6</v>
@@ -7352,7 +9615,7 @@
       <c r="U13">
         <v>0</v>
       </c>
-      <c r="Y13" s="11">
+      <c r="Y13" s="8">
         <v>900</v>
       </c>
       <c r="Z13">
@@ -7367,13 +9630,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>113</v>
+        <v>138</v>
       </c>
       <c r="C14">
         <v>1</v>
       </c>
       <c r="D14" t="s">
-        <v>113</v>
+        <v>138</v>
       </c>
       <c r="E14">
         <v>7</v>
@@ -7426,7 +9689,7 @@
       <c r="U14">
         <v>0</v>
       </c>
-      <c r="Y14" s="11">
+      <c r="Y14" s="8">
         <v>480</v>
       </c>
       <c r="Z14">
@@ -7441,13 +9704,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>114</v>
+        <v>139</v>
       </c>
       <c r="C15">
         <v>1</v>
       </c>
       <c r="D15" t="s">
-        <v>114</v>
+        <v>139</v>
       </c>
       <c r="E15">
         <v>8</v>
@@ -7500,7 +9763,7 @@
       <c r="U15">
         <v>0</v>
       </c>
-      <c r="Y15" s="11">
+      <c r="Y15" s="8">
         <v>1800</v>
       </c>
       <c r="Z15">
@@ -7515,13 +9778,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>115</v>
+        <v>140</v>
       </c>
       <c r="C16">
         <v>1</v>
       </c>
       <c r="D16" t="s">
-        <v>115</v>
+        <v>140</v>
       </c>
       <c r="E16">
         <v>9</v>
@@ -7574,7 +9837,7 @@
       <c r="U16">
         <v>0</v>
       </c>
-      <c r="Y16" s="11">
+      <c r="Y16" s="8">
         <v>900</v>
       </c>
       <c r="Z16">
@@ -7589,13 +9852,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>116</v>
+        <v>141</v>
       </c>
       <c r="C17">
         <v>1</v>
       </c>
       <c r="D17" t="s">
-        <v>116</v>
+        <v>141</v>
       </c>
       <c r="E17">
         <v>10</v>
@@ -7648,7 +9911,7 @@
       <c r="U17">
         <v>0</v>
       </c>
-      <c r="Y17" s="11">
+      <c r="Y17" s="8">
         <v>900</v>
       </c>
       <c r="Z17">
@@ -7663,13 +9926,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>117</v>
+        <v>142</v>
       </c>
       <c r="C18">
         <v>1</v>
       </c>
       <c r="D18" t="s">
-        <v>117</v>
+        <v>142</v>
       </c>
       <c r="E18">
         <v>10</v>
@@ -7722,7 +9985,7 @@
       <c r="U18">
         <v>0</v>
       </c>
-      <c r="Y18" s="11">
+      <c r="Y18" s="8">
         <v>900</v>
       </c>
       <c r="Z18">
@@ -7737,13 +10000,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>118</v>
+        <v>143</v>
       </c>
       <c r="C19">
         <v>1</v>
       </c>
       <c r="D19" t="s">
-        <v>118</v>
+        <v>143</v>
       </c>
       <c r="E19">
         <v>13</v>
@@ -7796,7 +10059,7 @@
       <c r="U19">
         <v>0</v>
       </c>
-      <c r="Y19" s="11">
+      <c r="Y19" s="8">
         <v>600</v>
       </c>
       <c r="Z19">
@@ -7811,13 +10074,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>119</v>
+        <v>144</v>
       </c>
       <c r="C20">
         <v>1</v>
       </c>
       <c r="D20" t="s">
-        <v>119</v>
+        <v>144</v>
       </c>
       <c r="E20">
         <v>14</v>
@@ -7870,7 +10133,7 @@
       <c r="U20">
         <v>0</v>
       </c>
-      <c r="Y20" s="11">
+      <c r="Y20" s="8">
         <v>600</v>
       </c>
       <c r="Z20">
@@ -7885,13 +10148,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>120</v>
+        <v>145</v>
       </c>
       <c r="C21">
         <v>1</v>
       </c>
       <c r="D21" t="s">
-        <v>120</v>
+        <v>145</v>
       </c>
       <c r="E21">
         <v>15</v>
@@ -7944,7 +10207,7 @@
       <c r="U21">
         <v>0</v>
       </c>
-      <c r="Y21" s="11">
+      <c r="Y21" s="8">
         <v>900</v>
       </c>
       <c r="Z21">
@@ -7959,13 +10222,13 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>121</v>
+        <v>146</v>
       </c>
       <c r="C22">
         <v>1</v>
       </c>
       <c r="D22" t="s">
-        <v>121</v>
+        <v>146</v>
       </c>
       <c r="E22">
         <v>16</v>
@@ -8018,7 +10281,7 @@
       <c r="U22">
         <v>0</v>
       </c>
-      <c r="Y22" s="11">
+      <c r="Y22" s="8">
         <v>500</v>
       </c>
       <c r="Z22">
@@ -8033,13 +10296,13 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>122</v>
+        <v>147</v>
       </c>
       <c r="C23">
         <v>1</v>
       </c>
       <c r="D23" t="s">
-        <v>122</v>
+        <v>147</v>
       </c>
       <c r="E23">
         <v>16</v>
@@ -8092,7 +10355,7 @@
       <c r="U23">
         <v>0</v>
       </c>
-      <c r="Y23" s="11">
+      <c r="Y23" s="8">
         <v>500</v>
       </c>
       <c r="Z23">
@@ -8107,13 +10370,13 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>123</v>
+        <v>148</v>
       </c>
       <c r="C24">
         <v>1</v>
       </c>
       <c r="D24" t="s">
-        <v>123</v>
+        <v>148</v>
       </c>
       <c r="E24">
         <v>16</v>
@@ -8166,7 +10429,7 @@
       <c r="U24">
         <v>0</v>
       </c>
-      <c r="Y24" s="11">
+      <c r="Y24" s="8">
         <v>600</v>
       </c>
       <c r="Z24">
@@ -8181,13 +10444,13 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>124</v>
+        <v>149</v>
       </c>
       <c r="C25">
         <v>1</v>
       </c>
       <c r="D25" t="s">
-        <v>124</v>
+        <v>149</v>
       </c>
       <c r="E25">
         <v>16</v>
@@ -8240,7 +10503,7 @@
       <c r="U25">
         <v>0</v>
       </c>
-      <c r="Y25" s="11">
+      <c r="Y25" s="8">
         <v>600</v>
       </c>
       <c r="Z25">
@@ -8255,13 +10518,13 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="C26">
         <v>1</v>
       </c>
       <c r="D26" t="s">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="E26">
         <v>17</v>
@@ -8314,7 +10577,7 @@
       <c r="U26">
         <v>0</v>
       </c>
-      <c r="Y26" s="11">
+      <c r="Y26" s="8">
         <v>600</v>
       </c>
       <c r="Z26">
@@ -8329,13 +10592,13 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>126</v>
+        <v>151</v>
       </c>
       <c r="C27">
         <v>1</v>
       </c>
       <c r="D27" t="s">
-        <v>126</v>
+        <v>151</v>
       </c>
       <c r="E27">
         <v>17</v>
@@ -8388,7 +10651,7 @@
       <c r="U27">
         <v>0</v>
       </c>
-      <c r="Y27" s="11">
+      <c r="Y27" s="8">
         <v>600</v>
       </c>
       <c r="Z27">
@@ -8403,13 +10666,13 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>127</v>
+        <v>152</v>
       </c>
       <c r="C28">
         <v>1</v>
       </c>
       <c r="D28" t="s">
-        <v>127</v>
+        <v>152</v>
       </c>
       <c r="E28">
         <v>21</v>
@@ -8462,7 +10725,7 @@
       <c r="U28">
         <v>0</v>
       </c>
-      <c r="Y28" s="11">
+      <c r="Y28" s="8">
         <v>600</v>
       </c>
       <c r="Z28">
@@ -8477,13 +10740,13 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>128</v>
+        <v>153</v>
       </c>
       <c r="C29">
         <v>1</v>
       </c>
       <c r="D29" t="s">
-        <v>128</v>
+        <v>153</v>
       </c>
       <c r="E29">
         <v>22</v>
@@ -8536,7 +10799,7 @@
       <c r="U29">
         <v>0</v>
       </c>
-      <c r="Y29" s="11">
+      <c r="Y29" s="8">
         <v>600</v>
       </c>
       <c r="Z29">
@@ -8551,13 +10814,13 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>129</v>
+        <v>154</v>
       </c>
       <c r="C30">
         <v>1</v>
       </c>
       <c r="D30" t="s">
-        <v>129</v>
+        <v>154</v>
       </c>
       <c r="E30">
         <v>23</v>
@@ -8610,7 +10873,7 @@
       <c r="U30">
         <v>0</v>
       </c>
-      <c r="Y30" s="11">
+      <c r="Y30" s="8">
         <v>600</v>
       </c>
       <c r="Z30">
@@ -8625,13 +10888,13 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>130</v>
+        <v>155</v>
       </c>
       <c r="C31">
         <v>1</v>
       </c>
       <c r="D31" t="s">
-        <v>130</v>
+        <v>155</v>
       </c>
       <c r="E31">
         <v>25</v>
@@ -8684,7 +10947,7 @@
       <c r="U31">
         <v>0</v>
       </c>
-      <c r="Y31" s="11">
+      <c r="Y31" s="8">
         <v>600</v>
       </c>
       <c r="Z31">
@@ -8699,13 +10962,13 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>131</v>
+        <v>156</v>
       </c>
       <c r="C32">
         <v>1</v>
       </c>
       <c r="D32" t="s">
-        <v>131</v>
+        <v>156</v>
       </c>
       <c r="E32">
         <v>26</v>
@@ -8758,7 +11021,7 @@
       <c r="U32">
         <v>0</v>
       </c>
-      <c r="Y32" s="11">
+      <c r="Y32" s="8">
         <v>600</v>
       </c>
       <c r="Z32">
@@ -8773,13 +11036,13 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>132</v>
+        <v>157</v>
       </c>
       <c r="C33">
         <v>1</v>
       </c>
       <c r="D33" t="s">
-        <v>132</v>
+        <v>157</v>
       </c>
       <c r="E33">
         <v>26</v>
@@ -8832,7 +11095,7 @@
       <c r="U33">
         <v>0</v>
       </c>
-      <c r="Y33" s="11">
+      <c r="Y33" s="8">
         <v>900</v>
       </c>
       <c r="Z33">
@@ -8847,13 +11110,13 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>133</v>
+        <v>158</v>
       </c>
       <c r="C34">
         <v>1</v>
       </c>
       <c r="D34" t="s">
-        <v>133</v>
+        <v>158</v>
       </c>
       <c r="E34">
         <v>26</v>
@@ -8906,7 +11169,7 @@
       <c r="U34">
         <v>0</v>
       </c>
-      <c r="Y34" s="11">
+      <c r="Y34" s="8">
         <v>900</v>
       </c>
       <c r="Z34">
@@ -8921,13 +11184,13 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>134</v>
+        <v>159</v>
       </c>
       <c r="C35">
         <v>1</v>
       </c>
       <c r="D35" t="s">
-        <v>134</v>
+        <v>159</v>
       </c>
       <c r="E35">
         <v>28</v>
@@ -8980,7 +11243,7 @@
       <c r="U35">
         <v>0</v>
       </c>
-      <c r="Y35" s="11">
+      <c r="Y35" s="8">
         <v>900</v>
       </c>
       <c r="Z35">
@@ -8995,13 +11258,13 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>135</v>
+        <v>160</v>
       </c>
       <c r="C36">
         <v>1</v>
       </c>
       <c r="D36" t="s">
-        <v>135</v>
+        <v>160</v>
       </c>
       <c r="E36">
         <v>2</v>
@@ -9054,7 +11317,7 @@
       <c r="U36">
         <v>0</v>
       </c>
-      <c r="Y36" s="11">
+      <c r="Y36" s="8">
         <v>900</v>
       </c>
       <c r="Z36">
@@ -9069,13 +11332,13 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>136</v>
+        <v>161</v>
       </c>
       <c r="C37">
         <v>1</v>
       </c>
       <c r="D37" t="s">
-        <v>136</v>
+        <v>161</v>
       </c>
       <c r="E37">
         <v>31</v>
@@ -9128,7 +11391,7 @@
       <c r="U37">
         <v>0</v>
       </c>
-      <c r="Y37" s="11">
+      <c r="Y37" s="8">
         <v>600</v>
       </c>
       <c r="Z37">
@@ -9143,13 +11406,13 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>137</v>
+        <v>162</v>
       </c>
       <c r="C38">
         <v>1</v>
       </c>
       <c r="D38" t="s">
-        <v>137</v>
+        <v>162</v>
       </c>
       <c r="E38">
         <v>10</v>
@@ -9202,7 +11465,7 @@
       <c r="U38">
         <v>0</v>
       </c>
-      <c r="Y38" s="11">
+      <c r="Y38" s="8">
         <v>900</v>
       </c>
       <c r="Z38">
@@ -9217,13 +11480,13 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>138</v>
+        <v>163</v>
       </c>
       <c r="C39">
         <v>1</v>
       </c>
       <c r="D39" t="s">
-        <v>138</v>
+        <v>163</v>
       </c>
       <c r="E39">
         <v>12</v>
@@ -9276,7 +11539,7 @@
       <c r="U39">
         <v>0</v>
       </c>
-      <c r="Y39" s="11">
+      <c r="Y39" s="8">
         <v>600</v>
       </c>
       <c r="Z39">
@@ -9291,13 +11554,13 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>139</v>
+        <v>164</v>
       </c>
       <c r="C40">
         <v>1</v>
       </c>
       <c r="D40" t="s">
-        <v>139</v>
+        <v>164</v>
       </c>
       <c r="E40">
         <v>12</v>
@@ -9350,7 +11613,7 @@
       <c r="U40">
         <v>0</v>
       </c>
-      <c r="Y40" s="11">
+      <c r="Y40" s="8">
         <v>900</v>
       </c>
       <c r="Z40">
@@ -9365,13 +11628,13 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>140</v>
+        <v>165</v>
       </c>
       <c r="C41">
         <v>1</v>
       </c>
       <c r="D41" t="s">
-        <v>140</v>
+        <v>165</v>
       </c>
       <c r="E41">
         <v>19</v>
@@ -9424,7 +11687,7 @@
       <c r="U41">
         <v>0</v>
       </c>
-      <c r="Y41" s="11">
+      <c r="Y41" s="8">
         <v>600</v>
       </c>
       <c r="Z41">
@@ -9439,13 +11702,13 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>141</v>
+        <v>166</v>
       </c>
       <c r="C42">
         <v>1</v>
       </c>
       <c r="D42" t="s">
-        <v>141</v>
+        <v>166</v>
       </c>
       <c r="E42">
         <v>19</v>
@@ -9498,7 +11761,7 @@
       <c r="U42">
         <v>0</v>
       </c>
-      <c r="Y42" s="11">
+      <c r="Y42" s="8">
         <v>900</v>
       </c>
       <c r="Z42">
@@ -9513,13 +11776,13 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>142</v>
+        <v>167</v>
       </c>
       <c r="C43">
         <v>1</v>
       </c>
       <c r="D43" t="s">
-        <v>142</v>
+        <v>167</v>
       </c>
       <c r="E43">
         <v>20</v>
@@ -9572,7 +11835,7 @@
       <c r="U43">
         <v>0</v>
       </c>
-      <c r="Y43" s="11">
+      <c r="Y43" s="8">
         <v>600</v>
       </c>
       <c r="Z43">
@@ -9587,13 +11850,13 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>143</v>
+        <v>168</v>
       </c>
       <c r="C44">
         <v>1</v>
       </c>
       <c r="D44" t="s">
-        <v>143</v>
+        <v>168</v>
       </c>
       <c r="E44">
         <v>22</v>
@@ -9646,7 +11909,7 @@
       <c r="U44">
         <v>0</v>
       </c>
-      <c r="Y44" s="11">
+      <c r="Y44" s="8">
         <v>600</v>
       </c>
       <c r="Z44">
@@ -9661,13 +11924,13 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>144</v>
+        <v>169</v>
       </c>
       <c r="C45">
         <v>1</v>
       </c>
       <c r="D45" t="s">
-        <v>144</v>
+        <v>169</v>
       </c>
       <c r="E45">
         <v>23</v>
@@ -9720,7 +11983,7 @@
       <c r="U45">
         <v>0</v>
       </c>
-      <c r="Y45" s="11">
+      <c r="Y45" s="8">
         <v>600</v>
       </c>
       <c r="Z45">
@@ -9735,13 +11998,13 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>145</v>
+        <v>170</v>
       </c>
       <c r="C46">
         <v>1</v>
       </c>
       <c r="D46" t="s">
-        <v>145</v>
+        <v>170</v>
       </c>
       <c r="E46">
         <v>25</v>
@@ -9794,7 +12057,7 @@
       <c r="U46">
         <v>0</v>
       </c>
-      <c r="Y46" s="11">
+      <c r="Y46" s="8">
         <v>600</v>
       </c>
       <c r="Z46">
@@ -9809,13 +12072,13 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>146</v>
+        <v>171</v>
       </c>
       <c r="C47">
         <v>1</v>
       </c>
       <c r="D47" t="s">
-        <v>146</v>
+        <v>171</v>
       </c>
       <c r="E47">
         <v>29</v>
@@ -9868,7 +12131,7 @@
       <c r="U47">
         <v>0</v>
       </c>
-      <c r="Y47" s="11">
+      <c r="Y47" s="8">
         <v>1200</v>
       </c>
       <c r="Z47">
@@ -9879,7 +12142,7 @@
       </c>
     </row>
     <row r="50" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E50" s="10"/>
+      <c r="E50" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9893,16 +12156,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
@@ -9916,7 +12179,7 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>147</v>
+        <v>172</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
@@ -9930,7 +12193,7 @@
         <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>148</v>
+        <v>173</v>
       </c>
     </row>
   </sheetData>
@@ -9948,97 +12211,97 @@
   <sheetData>
     <row r="1" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>149</v>
+        <v>174</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>251</v>
+        <v>176</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>151</v>
+        <v>177</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>152</v>
+        <v>178</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>153</v>
+        <v>179</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>154</v>
+        <v>180</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>155</v>
+        <v>181</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>156</v>
+        <v>182</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>157</v>
+        <v>183</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>158</v>
+        <v>184</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>253</v>
+        <v>185</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>254</v>
+        <v>186</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>159</v>
+        <v>187</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>160</v>
+        <v>188</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>161</v>
+        <v>189</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>162</v>
+        <v>190</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>163</v>
+        <v>191</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>164</v>
+        <v>192</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>165</v>
+        <v>193</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>166</v>
+        <v>194</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>167</v>
+        <v>195</v>
       </c>
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
@@ -10046,13 +12309,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>168</v>
+        <v>15</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>168</v>
+        <v>15</v>
       </c>
       <c r="E2">
         <v>31</v>
@@ -10061,7 +12324,7 @@
         <v>2</v>
       </c>
       <c r="G2" t="s">
-        <v>268</v>
+        <v>196</v>
       </c>
       <c r="I2">
         <v>836</v>
@@ -10076,7 +12339,7 @@
         <v>0</v>
       </c>
       <c r="M2">
-        <v>6.0600000000000005</v>
+        <v>6.06</v>
       </c>
       <c r="N2">
         <v>3.229665071770335E-3</v>
@@ -10138,13 +12401,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>169</v>
+        <v>17</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>169</v>
+        <v>17</v>
       </c>
       <c r="E3">
         <v>32</v>
@@ -10153,7 +12416,7 @@
         <v>3</v>
       </c>
       <c r="G3" t="s">
-        <v>268</v>
+        <v>196</v>
       </c>
       <c r="I3">
         <v>843.7</v>
@@ -10230,13 +12493,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>170</v>
+        <v>19</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
       <c r="D4" t="s">
-        <v>170</v>
+        <v>19</v>
       </c>
       <c r="E4">
         <v>33</v>
@@ -10245,7 +12508,7 @@
         <v>4</v>
       </c>
       <c r="G4" t="s">
-        <v>268</v>
+        <v>196</v>
       </c>
       <c r="I4">
         <v>1174.8</v>
@@ -10322,13 +12585,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>171</v>
+        <v>21</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>171</v>
+        <v>21</v>
       </c>
       <c r="E5">
         <v>34</v>
@@ -10337,7 +12600,7 @@
         <v>5</v>
       </c>
       <c r="G5" t="s">
-        <v>268</v>
+        <v>196</v>
       </c>
       <c r="I5">
         <v>1080.2</v>
@@ -10414,13 +12677,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>172</v>
+        <v>23</v>
       </c>
       <c r="C6">
         <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>172</v>
+        <v>23</v>
       </c>
       <c r="E6">
         <v>36</v>
@@ -10429,7 +12692,7 @@
         <v>7</v>
       </c>
       <c r="G6" t="s">
-        <v>268</v>
+        <v>196</v>
       </c>
       <c r="I6">
         <v>1025.2</v>
@@ -10506,13 +12769,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>173</v>
+        <v>25</v>
       </c>
       <c r="C7">
         <v>1</v>
       </c>
       <c r="D7" t="s">
-        <v>173</v>
+        <v>25</v>
       </c>
       <c r="E7">
         <v>39</v>
@@ -10521,7 +12784,7 @@
         <v>10</v>
       </c>
       <c r="G7" t="s">
-        <v>268</v>
+        <v>196</v>
       </c>
       <c r="I7">
         <v>1199</v>
@@ -10600,94 +12863,93 @@
       <c r="A10" s="1"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7388A490-0195-AD4B-9DED-7B8527B5ECA5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:Z18"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>149</v>
+        <v>174</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>251</v>
+        <v>176</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>252</v>
+        <v>197</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>156</v>
+        <v>182</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>267</v>
+        <v>198</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>152</v>
+        <v>178</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>151</v>
+        <v>177</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>253</v>
+        <v>185</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>254</v>
+        <v>186</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>255</v>
+        <v>199</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>256</v>
+        <v>200</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>257</v>
+        <v>201</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>258</v>
+        <v>202</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>259</v>
+        <v>203</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>260</v>
+        <v>204</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>261</v>
+        <v>205</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>262</v>
+        <v>206</v>
       </c>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.2">
@@ -10695,13 +12957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>263</v>
+        <v>207</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>263</v>
+        <v>207</v>
       </c>
       <c r="E2">
         <v>30</v>
@@ -10709,9 +12971,6 @@
       <c r="F2">
         <v>1</v>
       </c>
-      <c r="G2" t="s">
-        <v>268</v>
-      </c>
       <c r="H2">
         <v>1040</v>
       </c>
@@ -10719,7 +12978,7 @@
         <v>50</v>
       </c>
       <c r="J2">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="K2">
         <v>20</v>
@@ -10728,7 +12987,7 @@
         <v>0</v>
       </c>
       <c r="M2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N2">
         <v>2</v>
@@ -10775,13 +13034,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>264</v>
+        <v>208</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>264</v>
+        <v>208</v>
       </c>
       <c r="E3">
         <v>35</v>
@@ -10789,9 +13048,6 @@
       <c r="F3">
         <v>6</v>
       </c>
-      <c r="G3" t="s">
-        <v>268</v>
-      </c>
       <c r="H3">
         <v>1085.7</v>
       </c>
@@ -10799,7 +13055,7 @@
         <v>50</v>
       </c>
       <c r="J3">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="K3">
         <v>20</v>
@@ -10808,7 +13064,7 @@
         <v>0</v>
       </c>
       <c r="M3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N3">
         <v>2</v>
@@ -10855,13 +13111,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>265</v>
+        <v>209</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
       <c r="D4" t="s">
-        <v>265</v>
+        <v>209</v>
       </c>
       <c r="E4">
         <v>37</v>
@@ -10869,9 +13125,6 @@
       <c r="F4">
         <v>8</v>
       </c>
-      <c r="G4" t="s">
-        <v>268</v>
-      </c>
       <c r="H4">
         <v>970.2</v>
       </c>
@@ -10879,7 +13132,7 @@
         <v>50</v>
       </c>
       <c r="J4">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="K4">
         <v>20</v>
@@ -10888,7 +13141,7 @@
         <v>0</v>
       </c>
       <c r="M4">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N4">
         <v>2</v>
@@ -10935,13 +13188,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>266</v>
+        <v>210</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>266</v>
+        <v>210</v>
       </c>
       <c r="E5">
         <v>38</v>
@@ -10949,9 +13202,6 @@
       <c r="F5">
         <v>9</v>
       </c>
-      <c r="G5" t="s">
-        <v>268</v>
-      </c>
       <c r="H5">
         <v>1684.1</v>
       </c>
@@ -10959,7 +13209,7 @@
         <v>50</v>
       </c>
       <c r="J5">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="K5">
         <v>20</v>
@@ -10968,7 +13218,7 @@
         <v>0</v>
       </c>
       <c r="M5">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N5">
         <v>2</v>
@@ -11010,21 +13260,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:26" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="15" spans="1:26" ht="24" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="J15" s="7"/>
-    </row>
-    <row r="16" spans="1:26" ht="25" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="J16" s="8"/>
-    </row>
-    <row r="17" spans="10:10" ht="24" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="J17" s="9"/>
-    </row>
-    <row r="18" spans="10:10" ht="24" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="J18" s="9"/>
-    </row>
+    <row r="14" spans="1:26" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="15" spans="1:26" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="16" spans="1:26" ht="25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="17" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="18" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data_generation/andes_cases/ieee39_full_ibrs.xlsx
+++ b/data_generation/andes_cases/ieee39_full_ibrs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cloud9/Desktop/ETH Project/Working folder/03_Code/vis-ml/data_generation/andes_cases/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F27BE91F-D6FB-914E-9DF7-0A469826DB5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{000C107F-F3C4-F340-9EA3-519C164FE7E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20" yWindow="760" windowWidth="30240" windowHeight="17180" firstSheet="1" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="15000" windowHeight="18900" firstSheet="2" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Bus" sheetId="1" r:id="rId1"/>
@@ -1239,7 +1239,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1264,7 +1264,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4002,7 +4001,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
-  <dimension ref="A1:U11"/>
+  <dimension ref="A1:U7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.2">
@@ -4279,18 +4278,6 @@
       <c r="U7">
         <v>345</v>
       </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="Q9" s="10"/>
-      <c r="R9" s="10"/>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="Q10" s="10"/>
-      <c r="R10" s="10"/>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="Q11" s="10"/>
-      <c r="R11" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7137,7 +7124,7 @@
         <v>0.8</v>
       </c>
       <c r="K2">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
@@ -7207,7 +7194,7 @@
         <v>0.8</v>
       </c>
       <c r="K4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
@@ -7242,7 +7229,7 @@
         <v>0.8</v>
       </c>
       <c r="K5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
@@ -7277,7 +7264,7 @@
         <v>0.8</v>
       </c>
       <c r="K6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
@@ -7312,7 +7299,7 @@
         <v>0.8</v>
       </c>
       <c r="K7">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
@@ -7347,7 +7334,7 @@
         <v>0.8</v>
       </c>
       <c r="K8">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
@@ -7382,7 +7369,7 @@
         <v>0.8</v>
       </c>
       <c r="K9">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.2">
@@ -7417,7 +7404,7 @@
         <v>0.8</v>
       </c>
       <c r="K10">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.2">
@@ -7452,7 +7439,7 @@
         <v>0.8</v>
       </c>
       <c r="K11">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.2">
@@ -7487,7 +7474,7 @@
         <v>0.8</v>
       </c>
       <c r="K12">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
@@ -7522,7 +7509,7 @@
         <v>0.8</v>
       </c>
       <c r="K13">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.2">
@@ -7557,7 +7544,7 @@
         <v>0.8</v>
       </c>
       <c r="K14">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.2">
@@ -7592,7 +7579,7 @@
         <v>0.8</v>
       </c>
       <c r="K15">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.2">
@@ -7627,7 +7614,7 @@
         <v>0.8</v>
       </c>
       <c r="K16">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.2">
@@ -7732,7 +7719,7 @@
         <v>0.8</v>
       </c>
       <c r="K19">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.2">
@@ -10292,67 +10279,67 @@
       </c>
     </row>
     <row r="23" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A23" s="1">
+      <c r="A23" s="3">
         <v>21</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="C23">
-        <v>1</v>
-      </c>
-      <c r="D23" t="s">
+      <c r="C23" s="4">
+        <v>1</v>
+      </c>
+      <c r="D23" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="E23">
+      <c r="E23" s="4">
         <v>16</v>
       </c>
-      <c r="F23">
+      <c r="F23" s="4">
         <v>19</v>
       </c>
-      <c r="G23">
+      <c r="G23" s="4">
         <v>500</v>
       </c>
-      <c r="H23">
+      <c r="H23" s="4">
         <v>50</v>
       </c>
-      <c r="I23">
+      <c r="I23" s="4">
         <v>345</v>
       </c>
-      <c r="J23">
+      <c r="J23" s="4">
         <v>345</v>
       </c>
-      <c r="K23">
+      <c r="K23" s="4">
         <v>1.6000000000000001E-3</v>
       </c>
-      <c r="L23">
+      <c r="L23" s="4">
         <v>1.95E-2</v>
       </c>
-      <c r="M23">
+      <c r="M23" s="4">
         <v>0.30399999999999999</v>
       </c>
-      <c r="N23">
-        <v>0</v>
-      </c>
-      <c r="O23">
-        <v>0</v>
-      </c>
-      <c r="P23">
-        <v>0</v>
-      </c>
-      <c r="Q23">
-        <v>0</v>
-      </c>
-      <c r="R23">
-        <v>0</v>
-      </c>
-      <c r="S23">
-        <v>0</v>
-      </c>
-      <c r="T23">
-        <v>1</v>
-      </c>
-      <c r="U23">
+      <c r="N23" s="4">
+        <v>0</v>
+      </c>
+      <c r="O23" s="4">
+        <v>0</v>
+      </c>
+      <c r="P23" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="4">
+        <v>0</v>
+      </c>
+      <c r="R23" s="4">
+        <v>0</v>
+      </c>
+      <c r="S23" s="4">
+        <v>0</v>
+      </c>
+      <c r="T23" s="4">
+        <v>1</v>
+      </c>
+      <c r="U23" s="4">
         <v>0</v>
       </c>
       <c r="Y23" s="8">
@@ -11254,67 +11241,67 @@
       </c>
     </row>
     <row r="36" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A36" s="1">
+      <c r="A36" s="3">
         <v>34</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B36" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="C36">
-        <v>1</v>
-      </c>
-      <c r="D36" t="s">
+      <c r="C36" s="4">
+        <v>1</v>
+      </c>
+      <c r="D36" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="E36">
+      <c r="E36" s="4">
         <v>2</v>
       </c>
-      <c r="F36">
+      <c r="F36" s="4">
         <v>30</v>
       </c>
-      <c r="G36">
+      <c r="G36" s="4">
         <v>900</v>
       </c>
-      <c r="H36">
+      <c r="H36" s="4">
         <v>50</v>
       </c>
-      <c r="I36">
+      <c r="I36" s="4">
         <v>345</v>
       </c>
-      <c r="J36">
+      <c r="J36" s="4">
         <v>34.5</v>
       </c>
-      <c r="K36">
-        <v>0</v>
-      </c>
-      <c r="L36">
+      <c r="K36" s="4">
+        <v>0</v>
+      </c>
+      <c r="L36" s="4">
         <v>1.8100000000000002E-2</v>
       </c>
-      <c r="M36">
-        <v>0</v>
-      </c>
-      <c r="N36">
-        <v>0</v>
-      </c>
-      <c r="O36">
-        <v>0</v>
-      </c>
-      <c r="P36">
-        <v>0</v>
-      </c>
-      <c r="Q36">
-        <v>0</v>
-      </c>
-      <c r="R36">
-        <v>0</v>
-      </c>
-      <c r="S36">
-        <v>1</v>
-      </c>
-      <c r="T36">
+      <c r="M36" s="4">
+        <v>0</v>
+      </c>
+      <c r="N36" s="4">
+        <v>0</v>
+      </c>
+      <c r="O36" s="4">
+        <v>0</v>
+      </c>
+      <c r="P36" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q36" s="4">
+        <v>0</v>
+      </c>
+      <c r="R36" s="4">
+        <v>0</v>
+      </c>
+      <c r="S36" s="4">
+        <v>1</v>
+      </c>
+      <c r="T36" s="4">
         <v>1.0249999999999999</v>
       </c>
-      <c r="U36">
+      <c r="U36" s="4">
         <v>0</v>
       </c>
       <c r="Y36" s="8">
@@ -11328,67 +11315,67 @@
       </c>
     </row>
     <row r="37" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A37" s="1">
+      <c r="A37" s="3">
         <v>35</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B37" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="C37">
-        <v>1</v>
-      </c>
-      <c r="D37" t="s">
+      <c r="C37" s="4">
+        <v>1</v>
+      </c>
+      <c r="D37" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="E37">
+      <c r="E37" s="4">
         <v>31</v>
       </c>
-      <c r="F37">
+      <c r="F37" s="4">
         <v>6</v>
       </c>
-      <c r="G37">
+      <c r="G37" s="4">
         <v>600</v>
       </c>
-      <c r="H37">
+      <c r="H37" s="4">
         <v>50</v>
       </c>
-      <c r="I37">
+      <c r="I37" s="4">
         <v>34.5</v>
       </c>
-      <c r="J37">
+      <c r="J37" s="4">
         <v>345</v>
       </c>
-      <c r="K37">
-        <v>0</v>
-      </c>
-      <c r="L37">
+      <c r="K37" s="4">
+        <v>0</v>
+      </c>
+      <c r="L37" s="4">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="M37">
-        <v>0</v>
-      </c>
-      <c r="N37">
-        <v>0</v>
-      </c>
-      <c r="O37">
-        <v>0</v>
-      </c>
-      <c r="P37">
-        <v>0</v>
-      </c>
-      <c r="Q37">
-        <v>0</v>
-      </c>
-      <c r="R37">
-        <v>0</v>
-      </c>
-      <c r="S37">
-        <v>1</v>
-      </c>
-      <c r="T37">
+      <c r="M37" s="4">
+        <v>0</v>
+      </c>
+      <c r="N37" s="4">
+        <v>0</v>
+      </c>
+      <c r="O37" s="4">
+        <v>0</v>
+      </c>
+      <c r="P37" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q37" s="4">
+        <v>0</v>
+      </c>
+      <c r="R37" s="4">
+        <v>0</v>
+      </c>
+      <c r="S37" s="4">
+        <v>1</v>
+      </c>
+      <c r="T37" s="4">
         <v>0.9</v>
       </c>
-      <c r="U37">
+      <c r="U37" s="4">
         <v>0</v>
       </c>
       <c r="Y37" s="8">
@@ -11402,67 +11389,67 @@
       </c>
     </row>
     <row r="38" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A38" s="1">
+      <c r="A38" s="3">
         <v>36</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B38" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="C38">
-        <v>1</v>
-      </c>
-      <c r="D38" t="s">
+      <c r="C38" s="4">
+        <v>1</v>
+      </c>
+      <c r="D38" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="E38">
+      <c r="E38" s="4">
         <v>10</v>
       </c>
-      <c r="F38">
+      <c r="F38" s="4">
         <v>32</v>
       </c>
-      <c r="G38">
+      <c r="G38" s="4">
         <v>900</v>
       </c>
-      <c r="H38">
+      <c r="H38" s="4">
         <v>50</v>
       </c>
-      <c r="I38">
+      <c r="I38" s="4">
         <v>345</v>
       </c>
-      <c r="J38">
+      <c r="J38" s="4">
         <v>21</v>
       </c>
-      <c r="K38">
-        <v>0</v>
-      </c>
-      <c r="L38">
+      <c r="K38" s="4">
+        <v>0</v>
+      </c>
+      <c r="L38" s="4">
         <v>0.02</v>
       </c>
-      <c r="M38">
-        <v>0</v>
-      </c>
-      <c r="N38">
-        <v>0</v>
-      </c>
-      <c r="O38">
-        <v>0</v>
-      </c>
-      <c r="P38">
-        <v>0</v>
-      </c>
-      <c r="Q38">
-        <v>0</v>
-      </c>
-      <c r="R38">
-        <v>0</v>
-      </c>
-      <c r="S38">
-        <v>1</v>
-      </c>
-      <c r="T38">
+      <c r="M38" s="4">
+        <v>0</v>
+      </c>
+      <c r="N38" s="4">
+        <v>0</v>
+      </c>
+      <c r="O38" s="4">
+        <v>0</v>
+      </c>
+      <c r="P38" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q38" s="4">
+        <v>0</v>
+      </c>
+      <c r="R38" s="4">
+        <v>0</v>
+      </c>
+      <c r="S38" s="4">
+        <v>1</v>
+      </c>
+      <c r="T38" s="4">
         <v>1.07</v>
       </c>
-      <c r="U38">
+      <c r="U38" s="4">
         <v>0</v>
       </c>
       <c r="Y38" s="8">
@@ -11624,67 +11611,67 @@
       </c>
     </row>
     <row r="41" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A41" s="1">
+      <c r="A41" s="3">
         <v>39</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B41" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="C41">
-        <v>1</v>
-      </c>
-      <c r="D41" t="s">
+      <c r="C41" s="4">
+        <v>1</v>
+      </c>
+      <c r="D41" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="E41">
+      <c r="E41" s="4">
         <v>19</v>
       </c>
-      <c r="F41">
+      <c r="F41" s="4">
         <v>20</v>
       </c>
-      <c r="G41">
+      <c r="G41" s="4">
         <v>600</v>
       </c>
-      <c r="H41">
+      <c r="H41" s="4">
         <v>50</v>
       </c>
-      <c r="I41">
+      <c r="I41" s="4">
         <v>345</v>
       </c>
-      <c r="J41">
+      <c r="J41" s="4">
         <v>138</v>
       </c>
-      <c r="K41">
+      <c r="K41" s="4">
         <v>6.9999999999999999E-4</v>
       </c>
-      <c r="L41">
+      <c r="L41" s="4">
         <v>1.38E-2</v>
       </c>
-      <c r="M41">
-        <v>0</v>
-      </c>
-      <c r="N41">
-        <v>0</v>
-      </c>
-      <c r="O41">
-        <v>0</v>
-      </c>
-      <c r="P41">
-        <v>0</v>
-      </c>
-      <c r="Q41">
-        <v>0</v>
-      </c>
-      <c r="R41">
-        <v>0</v>
-      </c>
-      <c r="S41">
-        <v>1</v>
-      </c>
-      <c r="T41">
+      <c r="M41" s="4">
+        <v>0</v>
+      </c>
+      <c r="N41" s="4">
+        <v>0</v>
+      </c>
+      <c r="O41" s="4">
+        <v>0</v>
+      </c>
+      <c r="P41" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q41" s="4">
+        <v>0</v>
+      </c>
+      <c r="R41" s="4">
+        <v>0</v>
+      </c>
+      <c r="S41" s="4">
+        <v>1</v>
+      </c>
+      <c r="T41" s="4">
         <v>1.06</v>
       </c>
-      <c r="U41">
+      <c r="U41" s="4">
         <v>0</v>
       </c>
       <c r="Y41" s="8">
@@ -11698,67 +11685,67 @@
       </c>
     </row>
     <row r="42" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A42" s="1">
+      <c r="A42" s="3">
         <v>40</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B42" s="4" t="s">
         <v>166</v>
       </c>
-      <c r="C42">
-        <v>1</v>
-      </c>
-      <c r="D42" t="s">
+      <c r="C42" s="4">
+        <v>1</v>
+      </c>
+      <c r="D42" s="4" t="s">
         <v>166</v>
       </c>
-      <c r="E42">
+      <c r="E42" s="4">
         <v>19</v>
       </c>
-      <c r="F42">
+      <c r="F42" s="4">
         <v>33</v>
       </c>
-      <c r="G42">
+      <c r="G42" s="4">
         <v>900</v>
       </c>
-      <c r="H42">
+      <c r="H42" s="4">
         <v>50</v>
       </c>
-      <c r="I42">
+      <c r="I42" s="4">
         <v>345</v>
       </c>
-      <c r="J42">
+      <c r="J42" s="4">
         <v>21</v>
       </c>
-      <c r="K42">
+      <c r="K42" s="4">
         <v>6.9999999999999999E-4</v>
       </c>
-      <c r="L42">
+      <c r="L42" s="4">
         <v>1.4200000000000001E-2</v>
       </c>
-      <c r="M42">
-        <v>0</v>
-      </c>
-      <c r="N42">
-        <v>0</v>
-      </c>
-      <c r="O42">
-        <v>0</v>
-      </c>
-      <c r="P42">
-        <v>0</v>
-      </c>
-      <c r="Q42">
-        <v>0</v>
-      </c>
-      <c r="R42">
-        <v>0</v>
-      </c>
-      <c r="S42">
-        <v>1</v>
-      </c>
-      <c r="T42">
+      <c r="M42" s="4">
+        <v>0</v>
+      </c>
+      <c r="N42" s="4">
+        <v>0</v>
+      </c>
+      <c r="O42" s="4">
+        <v>0</v>
+      </c>
+      <c r="P42" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="4">
+        <v>0</v>
+      </c>
+      <c r="R42" s="4">
+        <v>0</v>
+      </c>
+      <c r="S42" s="4">
+        <v>1</v>
+      </c>
+      <c r="T42" s="4">
         <v>1.07</v>
       </c>
-      <c r="U42">
+      <c r="U42" s="4">
         <v>0</v>
       </c>
       <c r="Y42" s="8">
@@ -11772,67 +11759,67 @@
       </c>
     </row>
     <row r="43" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A43" s="1">
+      <c r="A43" s="3">
         <v>41</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B43" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="C43">
-        <v>1</v>
-      </c>
-      <c r="D43" t="s">
+      <c r="C43" s="4">
+        <v>1</v>
+      </c>
+      <c r="D43" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="E43">
+      <c r="E43" s="4">
         <v>20</v>
       </c>
-      <c r="F43">
+      <c r="F43" s="4">
         <v>34</v>
       </c>
-      <c r="G43">
+      <c r="G43" s="4">
         <v>600</v>
       </c>
-      <c r="H43">
+      <c r="H43" s="4">
         <v>50</v>
       </c>
-      <c r="I43">
+      <c r="I43" s="4">
         <v>138</v>
       </c>
-      <c r="J43">
+      <c r="J43" s="4">
         <v>15.5</v>
       </c>
-      <c r="K43">
+      <c r="K43" s="4">
         <v>8.9999999999999998E-4</v>
       </c>
-      <c r="L43">
+      <c r="L43" s="4">
         <v>1.7999999999999999E-2</v>
       </c>
-      <c r="M43">
-        <v>0</v>
-      </c>
-      <c r="N43">
-        <v>0</v>
-      </c>
-      <c r="O43">
-        <v>0</v>
-      </c>
-      <c r="P43">
-        <v>0</v>
-      </c>
-      <c r="Q43">
-        <v>0</v>
-      </c>
-      <c r="R43">
-        <v>0</v>
-      </c>
-      <c r="S43">
-        <v>1</v>
-      </c>
-      <c r="T43">
+      <c r="M43" s="4">
+        <v>0</v>
+      </c>
+      <c r="N43" s="4">
+        <v>0</v>
+      </c>
+      <c r="O43" s="4">
+        <v>0</v>
+      </c>
+      <c r="P43" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="4">
+        <v>0</v>
+      </c>
+      <c r="R43" s="4">
+        <v>0</v>
+      </c>
+      <c r="S43" s="4">
+        <v>1</v>
+      </c>
+      <c r="T43" s="4">
         <v>1.0089999999999999</v>
       </c>
-      <c r="U43">
+      <c r="U43" s="4">
         <v>0</v>
       </c>
       <c r="Y43" s="8">
@@ -11846,67 +11833,67 @@
       </c>
     </row>
     <row r="44" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A44" s="1">
+      <c r="A44" s="3">
         <v>42</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B44" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="C44">
-        <v>1</v>
-      </c>
-      <c r="D44" t="s">
+      <c r="C44" s="4">
+        <v>1</v>
+      </c>
+      <c r="D44" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="E44">
+      <c r="E44" s="4">
         <v>22</v>
       </c>
-      <c r="F44">
+      <c r="F44" s="4">
         <v>35</v>
       </c>
-      <c r="G44">
+      <c r="G44" s="4">
         <v>600</v>
       </c>
-      <c r="H44">
+      <c r="H44" s="4">
         <v>50</v>
       </c>
-      <c r="I44">
+      <c r="I44" s="4">
         <v>345</v>
       </c>
-      <c r="J44">
+      <c r="J44" s="4">
         <v>15.5</v>
       </c>
-      <c r="K44">
-        <v>0</v>
-      </c>
-      <c r="L44">
+      <c r="K44" s="4">
+        <v>0</v>
+      </c>
+      <c r="L44" s="4">
         <v>1.43E-2</v>
       </c>
-      <c r="M44">
-        <v>0</v>
-      </c>
-      <c r="N44">
-        <v>0</v>
-      </c>
-      <c r="O44">
-        <v>0</v>
-      </c>
-      <c r="P44">
-        <v>0</v>
-      </c>
-      <c r="Q44">
-        <v>0</v>
-      </c>
-      <c r="R44">
-        <v>0</v>
-      </c>
-      <c r="S44">
-        <v>1</v>
-      </c>
-      <c r="T44">
+      <c r="M44" s="4">
+        <v>0</v>
+      </c>
+      <c r="N44" s="4">
+        <v>0</v>
+      </c>
+      <c r="O44" s="4">
+        <v>0</v>
+      </c>
+      <c r="P44" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="4">
+        <v>0</v>
+      </c>
+      <c r="R44" s="4">
+        <v>0</v>
+      </c>
+      <c r="S44" s="4">
+        <v>1</v>
+      </c>
+      <c r="T44" s="4">
         <v>1.0249999999999999</v>
       </c>
-      <c r="U44">
+      <c r="U44" s="4">
         <v>0</v>
       </c>
       <c r="Y44" s="8">
@@ -11920,67 +11907,67 @@
       </c>
     </row>
     <row r="45" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A45" s="1">
+      <c r="A45" s="3">
         <v>43</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B45" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="C45">
-        <v>1</v>
-      </c>
-      <c r="D45" t="s">
+      <c r="C45" s="4">
+        <v>1</v>
+      </c>
+      <c r="D45" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="E45">
+      <c r="E45" s="4">
         <v>23</v>
       </c>
-      <c r="F45">
+      <c r="F45" s="4">
         <v>36</v>
       </c>
-      <c r="G45">
+      <c r="G45" s="4">
         <v>600</v>
       </c>
-      <c r="H45">
+      <c r="H45" s="4">
         <v>50</v>
       </c>
-      <c r="I45">
+      <c r="I45" s="4">
         <v>345</v>
       </c>
-      <c r="J45">
+      <c r="J45" s="4">
         <v>12.5</v>
       </c>
-      <c r="K45">
+      <c r="K45" s="4">
         <v>5.0000000000000001E-4</v>
       </c>
-      <c r="L45">
+      <c r="L45" s="4">
         <v>2.7199999999999998E-2</v>
       </c>
-      <c r="M45">
-        <v>0</v>
-      </c>
-      <c r="N45">
-        <v>0</v>
-      </c>
-      <c r="O45">
-        <v>0</v>
-      </c>
-      <c r="P45">
-        <v>0</v>
-      </c>
-      <c r="Q45">
-        <v>0</v>
-      </c>
-      <c r="R45">
-        <v>0</v>
-      </c>
-      <c r="S45">
-        <v>1</v>
-      </c>
-      <c r="T45">
-        <v>1</v>
-      </c>
-      <c r="U45">
+      <c r="M45" s="4">
+        <v>0</v>
+      </c>
+      <c r="N45" s="4">
+        <v>0</v>
+      </c>
+      <c r="O45" s="4">
+        <v>0</v>
+      </c>
+      <c r="P45" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="4">
+        <v>0</v>
+      </c>
+      <c r="R45" s="4">
+        <v>0</v>
+      </c>
+      <c r="S45" s="4">
+        <v>1</v>
+      </c>
+      <c r="T45" s="4">
+        <v>1</v>
+      </c>
+      <c r="U45" s="4">
         <v>0</v>
       </c>
       <c r="Y45" s="8">
@@ -11994,67 +11981,67 @@
       </c>
     </row>
     <row r="46" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A46" s="1">
+      <c r="A46" s="3">
         <v>44</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B46" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="C46">
-        <v>1</v>
-      </c>
-      <c r="D46" t="s">
+      <c r="C46" s="4">
+        <v>1</v>
+      </c>
+      <c r="D46" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="E46">
+      <c r="E46" s="4">
         <v>25</v>
       </c>
-      <c r="F46">
+      <c r="F46" s="4">
         <v>37</v>
       </c>
-      <c r="G46">
+      <c r="G46" s="4">
         <v>600</v>
       </c>
-      <c r="H46">
+      <c r="H46" s="4">
         <v>50</v>
       </c>
-      <c r="I46">
+      <c r="I46" s="4">
         <v>345</v>
       </c>
-      <c r="J46">
+      <c r="J46" s="4">
         <v>12.5</v>
       </c>
-      <c r="K46">
+      <c r="K46" s="4">
         <v>5.9999999999999995E-4</v>
       </c>
-      <c r="L46">
+      <c r="L46" s="4">
         <v>2.3199999999999998E-2</v>
       </c>
-      <c r="M46">
-        <v>0</v>
-      </c>
-      <c r="N46">
-        <v>0</v>
-      </c>
-      <c r="O46">
-        <v>0</v>
-      </c>
-      <c r="P46">
-        <v>0</v>
-      </c>
-      <c r="Q46">
-        <v>0</v>
-      </c>
-      <c r="R46">
-        <v>0</v>
-      </c>
-      <c r="S46">
-        <v>1</v>
-      </c>
-      <c r="T46">
+      <c r="M46" s="4">
+        <v>0</v>
+      </c>
+      <c r="N46" s="4">
+        <v>0</v>
+      </c>
+      <c r="O46" s="4">
+        <v>0</v>
+      </c>
+      <c r="P46" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="4">
+        <v>0</v>
+      </c>
+      <c r="R46" s="4">
+        <v>0</v>
+      </c>
+      <c r="S46" s="4">
+        <v>1</v>
+      </c>
+      <c r="T46" s="4">
         <v>1.0249999999999999</v>
       </c>
-      <c r="U46">
+      <c r="U46" s="4">
         <v>0</v>
       </c>
       <c r="Y46" s="8">
@@ -12068,67 +12055,67 @@
       </c>
     </row>
     <row r="47" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A47" s="1">
+      <c r="A47" s="3">
         <v>45</v>
       </c>
-      <c r="B47" t="s">
+      <c r="B47" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="C47">
-        <v>1</v>
-      </c>
-      <c r="D47" t="s">
+      <c r="C47" s="4">
+        <v>1</v>
+      </c>
+      <c r="D47" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="E47">
+      <c r="E47" s="4">
         <v>29</v>
       </c>
-      <c r="F47">
+      <c r="F47" s="4">
         <v>38</v>
       </c>
-      <c r="G47">
+      <c r="G47" s="4">
         <v>1200</v>
       </c>
-      <c r="H47">
+      <c r="H47" s="4">
         <v>50</v>
       </c>
-      <c r="I47">
+      <c r="I47" s="4">
         <v>345</v>
       </c>
-      <c r="J47">
+      <c r="J47" s="4">
         <v>34.5</v>
       </c>
-      <c r="K47">
+      <c r="K47" s="4">
         <v>8.0000000000000004E-4</v>
       </c>
-      <c r="L47">
+      <c r="L47" s="4">
         <v>1.5599999999999999E-2</v>
       </c>
-      <c r="M47">
-        <v>0</v>
-      </c>
-      <c r="N47">
-        <v>0</v>
-      </c>
-      <c r="O47">
-        <v>0</v>
-      </c>
-      <c r="P47">
-        <v>0</v>
-      </c>
-      <c r="Q47">
-        <v>0</v>
-      </c>
-      <c r="R47">
-        <v>0</v>
-      </c>
-      <c r="S47">
-        <v>1</v>
-      </c>
-      <c r="T47">
+      <c r="M47" s="4">
+        <v>0</v>
+      </c>
+      <c r="N47" s="4">
+        <v>0</v>
+      </c>
+      <c r="O47" s="4">
+        <v>0</v>
+      </c>
+      <c r="P47" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="4">
+        <v>0</v>
+      </c>
+      <c r="R47" s="4">
+        <v>0</v>
+      </c>
+      <c r="S47" s="4">
+        <v>1</v>
+      </c>
+      <c r="T47" s="4">
         <v>1.0249999999999999</v>
       </c>
-      <c r="U47">
+      <c r="U47" s="4">
         <v>0</v>
       </c>
       <c r="Y47" s="8">
@@ -12981,7 +12968,7 @@
         <v>0.01</v>
       </c>
       <c r="K2">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -13058,7 +13045,7 @@
         <v>0.01</v>
       </c>
       <c r="K3">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="L3">
         <v>0</v>
@@ -13135,7 +13122,7 @@
         <v>0.01</v>
       </c>
       <c r="K4">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="L4">
         <v>0</v>
@@ -13212,7 +13199,7 @@
         <v>0.01</v>
       </c>
       <c r="K5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="L5">
         <v>0</v>

--- a/data_generation/andes_cases/ieee39_full_ibrs.xlsx
+++ b/data_generation/andes_cases/ieee39_full_ibrs.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{000C107F-F3C4-F340-9EA3-519C164FE7E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="15000" windowHeight="18900" firstSheet="2" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="30240" windowHeight="18900" firstSheet="6" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Bus" sheetId="1" r:id="rId1"/>
